--- a/prices.xlsx
+++ b/prices.xlsx
@@ -464,10 +464,10 @@
         <v>1125.651733398438</v>
       </c>
       <c r="C2" t="n">
-        <v>780.8386840820312</v>
+        <v>780.838623046875</v>
       </c>
       <c r="D2" t="n">
-        <v>1186.7919921875</v>
+        <v>1186.791748046875</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>778.4051513671875</v>
       </c>
       <c r="D3" t="n">
-        <v>1163.5927734375</v>
+        <v>1163.592895507812</v>
       </c>
     </row>
     <row r="4">
@@ -489,10 +489,10 @@
         <v>45084</v>
       </c>
       <c r="B4" t="n">
-        <v>1135.148559570312</v>
+        <v>1135.148681640625</v>
       </c>
       <c r="C4" t="n">
-        <v>782.444580078125</v>
+        <v>782.4446411132812</v>
       </c>
       <c r="D4" t="n">
         <v>1172.644897460938</v>
@@ -509,7 +509,7 @@
         <v>782.9312744140625</v>
       </c>
       <c r="D5" t="n">
-        <v>1167.049926757812</v>
+        <v>1167.0498046875</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         <v>45086</v>
       </c>
       <c r="B6" t="n">
-        <v>1127.787353515625</v>
+        <v>1127.787475585938</v>
       </c>
       <c r="C6" t="n">
-        <v>783.8560791015625</v>
+        <v>783.8560180664062</v>
       </c>
       <c r="D6" t="n">
-        <v>1151.720336914062</v>
+        <v>1151.72021484375</v>
       </c>
     </row>
     <row r="7">
@@ -531,13 +531,13 @@
         <v>45089</v>
       </c>
       <c r="B7" t="n">
-        <v>1128.786987304688</v>
+        <v>1128.787109375</v>
       </c>
       <c r="C7" t="n">
         <v>779.0865478515625</v>
       </c>
       <c r="D7" t="n">
-        <v>1175.374267578125</v>
+        <v>1175.3740234375</v>
       </c>
     </row>
     <row r="8">
@@ -545,13 +545,13 @@
         <v>45090</v>
       </c>
       <c r="B8" t="n">
-        <v>1145.46337890625</v>
+        <v>1145.463256835938</v>
       </c>
       <c r="C8" t="n">
         <v>780.4005737304688</v>
       </c>
       <c r="D8" t="n">
-        <v>1187.110229492188</v>
+        <v>1187.1103515625</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>779.5488891601562</v>
       </c>
       <c r="D9" t="n">
-        <v>1183.061889648438</v>
+        <v>1183.061767578125</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         <v>769.961181640625</v>
       </c>
       <c r="D10" t="n">
-        <v>1170.68896484375</v>
+        <v>1170.688842773438</v>
       </c>
     </row>
     <row r="11">
@@ -587,13 +587,13 @@
         <v>45093</v>
       </c>
       <c r="B11" t="n">
-        <v>1171.159423828125</v>
+        <v>1171.159545898438</v>
       </c>
       <c r="C11" t="n">
-        <v>780.0355834960938</v>
+        <v>780.0355224609375</v>
       </c>
       <c r="D11" t="n">
-        <v>1175.101318359375</v>
+        <v>1175.101440429688</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>45096</v>
       </c>
       <c r="B12" t="n">
-        <v>1159.526977539062</v>
+        <v>1159.52685546875</v>
       </c>
       <c r="C12" t="n">
         <v>780.7169799804688</v>
@@ -618,10 +618,10 @@
         <v>1161.935180664062</v>
       </c>
       <c r="C13" t="n">
-        <v>782.3472900390625</v>
+        <v>782.3473510742188</v>
       </c>
       <c r="D13" t="n">
-        <v>1185.791137695312</v>
+        <v>1185.791259765625</v>
       </c>
     </row>
     <row r="14">
@@ -635,7 +635,7 @@
         <v>796.0231323242188</v>
       </c>
       <c r="D14" t="n">
-        <v>1182.1064453125</v>
+        <v>1182.106567382812</v>
       </c>
     </row>
     <row r="15">
@@ -671,13 +671,13 @@
         <v>45103</v>
       </c>
       <c r="B17" t="n">
-        <v>1133.967041015625</v>
+        <v>1133.967163085938</v>
       </c>
       <c r="C17" t="n">
-        <v>795.9988403320312</v>
+        <v>795.9989013671875</v>
       </c>
       <c r="D17" t="n">
-        <v>1155.723266601562</v>
+        <v>1155.72314453125</v>
       </c>
     </row>
     <row r="18">
@@ -685,13 +685,13 @@
         <v>45104</v>
       </c>
       <c r="B18" t="n">
-        <v>1134.376220703125</v>
+        <v>1134.376098632812</v>
       </c>
       <c r="C18" t="n">
-        <v>807.2169189453125</v>
+        <v>807.2169799804688</v>
       </c>
       <c r="D18" t="n">
-        <v>1163.729125976562</v>
+        <v>1163.729248046875</v>
       </c>
     </row>
     <row r="19">
@@ -713,13 +713,13 @@
         <v>45107</v>
       </c>
       <c r="B20" t="n">
-        <v>1158.822631835938</v>
+        <v>1158.822509765625</v>
       </c>
       <c r="C20" t="n">
-        <v>828.047119140625</v>
+        <v>828.0470581054688</v>
       </c>
       <c r="D20" t="n">
-        <v>1214.994873046875</v>
+        <v>1214.994750976562</v>
       </c>
     </row>
     <row r="21">
@@ -730,7 +730,7 @@
         <v>1188.562866210938</v>
       </c>
       <c r="C21" t="n">
-        <v>837.002197265625</v>
+        <v>837.0021362304688</v>
       </c>
       <c r="D21" t="n">
         <v>1213.357055664062</v>
@@ -744,7 +744,7 @@
         <v>1176.316772460938</v>
       </c>
       <c r="C22" t="n">
-        <v>841.0902709960938</v>
+        <v>841.0902099609375</v>
       </c>
       <c r="D22" t="n">
         <v>1223.77392578125</v>
@@ -755,7 +755,7 @@
         <v>45112</v>
       </c>
       <c r="B23" t="n">
-        <v>1174.385620117188</v>
+        <v>1174.3857421875</v>
       </c>
       <c r="C23" t="n">
         <v>814.3712768554688</v>
@@ -769,13 +769,13 @@
         <v>45113</v>
       </c>
       <c r="B24" t="n">
-        <v>1199.03662109375</v>
+        <v>1199.036743164062</v>
       </c>
       <c r="C24" t="n">
         <v>815.1986083984375</v>
       </c>
       <c r="D24" t="n">
-        <v>1222.63671875</v>
+        <v>1222.636596679688</v>
       </c>
     </row>
     <row r="25">
@@ -789,7 +789,7 @@
         <v>808.093017578125</v>
       </c>
       <c r="D25" t="n">
-        <v>1210.1728515625</v>
+        <v>1210.172729492188</v>
       </c>
     </row>
     <row r="26">
@@ -797,13 +797,13 @@
         <v>45117</v>
       </c>
       <c r="B26" t="n">
-        <v>1242.794799804688</v>
+        <v>1242.794921875</v>
       </c>
       <c r="C26" t="n">
-        <v>806.1705932617188</v>
+        <v>806.1705322265625</v>
       </c>
       <c r="D26" t="n">
-        <v>1209.217651367188</v>
+        <v>1209.217407226562</v>
       </c>
     </row>
     <row r="27">
@@ -811,13 +811,13 @@
         <v>45118</v>
       </c>
       <c r="B27" t="n">
-        <v>1256.267578125</v>
+        <v>1256.267700195312</v>
       </c>
       <c r="C27" t="n">
         <v>802.2527465820312</v>
       </c>
       <c r="D27" t="n">
-        <v>1226.912353515625</v>
+        <v>1226.91259765625</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>45119</v>
       </c>
       <c r="B28" t="n">
-        <v>1257.653564453125</v>
+        <v>1257.653686523438</v>
       </c>
       <c r="C28" t="n">
         <v>794.7334594726562</v>
@@ -839,13 +839,13 @@
         <v>45120</v>
       </c>
       <c r="B29" t="n">
-        <v>1246.407470703125</v>
+        <v>1246.4072265625</v>
       </c>
       <c r="C29" t="n">
-        <v>798.699951171875</v>
+        <v>798.6998901367188</v>
       </c>
       <c r="D29" t="n">
-        <v>1241.923706054688</v>
+        <v>1241.923583984375</v>
       </c>
     </row>
     <row r="30">
@@ -853,13 +853,13 @@
         <v>45121</v>
       </c>
       <c r="B30" t="n">
-        <v>1245.362182617188</v>
+        <v>1245.362426757812</v>
       </c>
       <c r="C30" t="n">
         <v>800.3546752929688</v>
       </c>
       <c r="D30" t="n">
-        <v>1297.283081054688</v>
+        <v>1297.282958984375</v>
       </c>
     </row>
     <row r="31">
@@ -884,7 +884,7 @@
         <v>1281.600219726562</v>
       </c>
       <c r="C32" t="n">
-        <v>816.415283203125</v>
+        <v>816.4153442382812</v>
       </c>
       <c r="D32" t="n">
         <v>1342.089111328125</v>
@@ -895,7 +895,7 @@
         <v>45126</v>
       </c>
       <c r="B33" t="n">
-        <v>1291.324340820312</v>
+        <v>1291.324462890625</v>
       </c>
       <c r="C33" t="n">
         <v>820.1141357421875</v>
@@ -909,13 +909,13 @@
         <v>45127</v>
       </c>
       <c r="B34" t="n">
-        <v>1289.760620117188</v>
+        <v>1289.760375976562</v>
       </c>
       <c r="C34" t="n">
         <v>821.8905639648438</v>
       </c>
       <c r="D34" t="n">
-        <v>1318.708251953125</v>
+        <v>1318.708129882812</v>
       </c>
     </row>
     <row r="35">
@@ -929,7 +929,7 @@
         <v>815.5635986328125</v>
       </c>
       <c r="D35" t="n">
-        <v>1211.446411132812</v>
+        <v>1211.446533203125</v>
       </c>
     </row>
     <row r="36">
@@ -937,13 +937,13 @@
         <v>45131</v>
       </c>
       <c r="B36" t="n">
-        <v>1224.554931640625</v>
+        <v>1224.554809570312</v>
       </c>
       <c r="C36" t="n">
-        <v>816.8533325195312</v>
+        <v>816.8533935546875</v>
       </c>
       <c r="D36" t="n">
-        <v>1215.995361328125</v>
+        <v>1215.995239257812</v>
       </c>
     </row>
     <row r="37">
@@ -957,7 +957,7 @@
         <v>825.7109985351562</v>
       </c>
       <c r="D37" t="n">
-        <v>1214.17578125</v>
+        <v>1214.175903320312</v>
       </c>
     </row>
     <row r="38">
@@ -979,13 +979,13 @@
         <v>45134</v>
       </c>
       <c r="B39" t="n">
-        <v>1232.087280273438</v>
+        <v>1232.087158203125</v>
       </c>
       <c r="C39" t="n">
         <v>814.2982177734375</v>
       </c>
       <c r="D39" t="n">
-        <v>1231.052001953125</v>
+        <v>1231.052124023438</v>
       </c>
     </row>
     <row r="40">
@@ -993,7 +993,7 @@
         <v>45135</v>
       </c>
       <c r="B40" t="n">
-        <v>1244.468505859375</v>
+        <v>1244.468627929688</v>
       </c>
       <c r="C40" t="n">
         <v>799.8680419921875</v>
@@ -1010,7 +1010,7 @@
         <v>1255.00390625</v>
       </c>
       <c r="C41" t="n">
-        <v>803.615478515625</v>
+        <v>803.6154174804688</v>
       </c>
       <c r="D41" t="n">
         <v>1233.371948242188</v>
@@ -1024,7 +1024,7 @@
         <v>1237.25634765625</v>
       </c>
       <c r="C42" t="n">
-        <v>808.993408203125</v>
+        <v>808.9933471679688</v>
       </c>
       <c r="D42" t="n">
         <v>1242.0146484375</v>
@@ -1038,10 +1038,10 @@
         <v>1224.0380859375</v>
       </c>
       <c r="C43" t="n">
-        <v>798.407958984375</v>
+        <v>798.4080200195312</v>
       </c>
       <c r="D43" t="n">
-        <v>1234.41796875</v>
+        <v>1234.418212890625</v>
       </c>
     </row>
     <row r="44">
@@ -1049,13 +1049,13 @@
         <v>45141</v>
       </c>
       <c r="B44" t="n">
-        <v>1218.893432617188</v>
+        <v>1218.893310546875</v>
       </c>
       <c r="C44" t="n">
         <v>792.6407470703125</v>
       </c>
       <c r="D44" t="n">
-        <v>1241.195922851562</v>
+        <v>1241.196044921875</v>
       </c>
     </row>
     <row r="45">
@@ -1069,7 +1069,7 @@
         <v>804.1021728515625</v>
       </c>
       <c r="D45" t="n">
-        <v>1253.97802734375</v>
+        <v>1253.978149414062</v>
       </c>
     </row>
     <row r="46">
@@ -1091,7 +1091,7 @@
         <v>45146</v>
       </c>
       <c r="B47" t="n">
-        <v>1235.016357421875</v>
+        <v>1235.016235351562</v>
       </c>
       <c r="C47" t="n">
         <v>802.9828491210938</v>
@@ -1105,7 +1105,7 @@
         <v>45147</v>
       </c>
       <c r="B48" t="n">
-        <v>1243.163940429688</v>
+        <v>1243.1640625</v>
       </c>
       <c r="C48" t="n">
         <v>803.2747802734375</v>
@@ -1133,13 +1133,13 @@
         <v>45149</v>
       </c>
       <c r="B50" t="n">
-        <v>1253.970092773438</v>
+        <v>1253.969970703125</v>
       </c>
       <c r="C50" t="n">
-        <v>787.846923828125</v>
+        <v>787.8468627929688</v>
       </c>
       <c r="D50" t="n">
-        <v>1248.064575195312</v>
+        <v>1248.064697265625</v>
       </c>
     </row>
     <row r="51">
@@ -1147,13 +1147,13 @@
         <v>45152</v>
       </c>
       <c r="B51" t="n">
-        <v>1268.788330078125</v>
+        <v>1268.788208007812</v>
       </c>
       <c r="C51" t="n">
-        <v>784.0020751953125</v>
+        <v>784.0021362304688</v>
       </c>
       <c r="D51" t="n">
-        <v>1267.806762695312</v>
+        <v>1267.806640625</v>
       </c>
     </row>
     <row r="52">
@@ -1175,13 +1175,13 @@
         <v>45155</v>
       </c>
       <c r="B53" t="n">
-        <v>1249.465576171875</v>
+        <v>1249.465454101562</v>
       </c>
       <c r="C53" t="n">
         <v>777.3831176757812</v>
       </c>
       <c r="D53" t="n">
-        <v>1284.182373046875</v>
+        <v>1284.182495117188</v>
       </c>
     </row>
     <row r="54">
@@ -1217,13 +1217,13 @@
         <v>45160</v>
       </c>
       <c r="B56" t="n">
-        <v>1244.689819335938</v>
+        <v>1244.68994140625</v>
       </c>
       <c r="C56" t="n">
         <v>770.2774658203125</v>
       </c>
       <c r="D56" t="n">
-        <v>1277.086303710938</v>
+        <v>1277.086181640625</v>
       </c>
     </row>
     <row r="57">
@@ -1231,13 +1231,13 @@
         <v>45161</v>
       </c>
       <c r="B57" t="n">
-        <v>1246.073364257812</v>
+        <v>1246.0732421875</v>
       </c>
       <c r="C57" t="n">
         <v>772.1755981445312</v>
       </c>
       <c r="D57" t="n">
-        <v>1280.907104492188</v>
+        <v>1280.9072265625</v>
       </c>
     </row>
     <row r="58">
@@ -1248,7 +1248,7 @@
         <v>1225.125854492188</v>
       </c>
       <c r="C58" t="n">
-        <v>768.622802734375</v>
+        <v>768.6227416992188</v>
       </c>
       <c r="D58" t="n">
         <v>1295.145141601562</v>
@@ -1279,7 +1279,7 @@
         <v>767.868408203125</v>
       </c>
       <c r="D60" t="n">
-        <v>1287.912353515625</v>
+        <v>1287.91259765625</v>
       </c>
     </row>
     <row r="61">
@@ -1290,10 +1290,10 @@
         <v>1195.755126953125</v>
       </c>
       <c r="C61" t="n">
-        <v>773.976318359375</v>
+        <v>773.9763793945312</v>
       </c>
       <c r="D61" t="n">
-        <v>1289.731811523438</v>
+        <v>1289.732055664062</v>
       </c>
     </row>
     <row r="62">
@@ -1301,7 +1301,7 @@
         <v>45168</v>
       </c>
       <c r="B62" t="n">
-        <v>1194.618774414062</v>
+        <v>1194.61865234375</v>
       </c>
       <c r="C62" t="n">
         <v>768.3307495117188</v>
@@ -1315,13 +1315,13 @@
         <v>45169</v>
       </c>
       <c r="B63" t="n">
-        <v>1189.15966796875</v>
+        <v>1189.159545898438</v>
       </c>
       <c r="C63" t="n">
         <v>764.80224609375</v>
       </c>
       <c r="D63" t="n">
-        <v>1305.926025390625</v>
+        <v>1305.92578125</v>
       </c>
     </row>
     <row r="64">
@@ -1332,7 +1332,7 @@
         <v>1191.950927734375</v>
       </c>
       <c r="C64" t="n">
-        <v>766.384033203125</v>
+        <v>766.3839721679688</v>
       </c>
       <c r="D64" t="n">
         <v>1313.56787109375</v>
@@ -1346,10 +1346,10 @@
         <v>1190.987426757812</v>
       </c>
       <c r="C65" t="n">
-        <v>771.1778564453125</v>
+        <v>771.1779174804688</v>
       </c>
       <c r="D65" t="n">
-        <v>1332.900512695312</v>
+        <v>1332.900390625</v>
       </c>
     </row>
     <row r="66">
@@ -1357,13 +1357,13 @@
         <v>45174</v>
       </c>
       <c r="B66" t="n">
-        <v>1197.36083984375</v>
+        <v>1197.360717773438</v>
       </c>
       <c r="C66" t="n">
-        <v>766.4813842773438</v>
+        <v>766.4814453125</v>
       </c>
       <c r="D66" t="n">
-        <v>1345.455444335938</v>
+        <v>1345.455322265625</v>
       </c>
     </row>
     <row r="67">
@@ -1371,7 +1371,7 @@
         <v>45175</v>
       </c>
       <c r="B67" t="n">
-        <v>1199.880249023438</v>
+        <v>1199.88037109375</v>
       </c>
       <c r="C67" t="n">
         <v>776.507080078125</v>
@@ -1385,13 +1385,13 @@
         <v>45176</v>
       </c>
       <c r="B68" t="n">
-        <v>1201.510620117188</v>
+        <v>1201.5107421875</v>
       </c>
       <c r="C68" t="n">
-        <v>783.977783203125</v>
+        <v>783.9777221679688</v>
       </c>
       <c r="D68" t="n">
-        <v>1333.901245117188</v>
+        <v>1333.901123046875</v>
       </c>
     </row>
     <row r="69">
@@ -1399,13 +1399,13 @@
         <v>45177</v>
       </c>
       <c r="B69" t="n">
-        <v>1209.51416015625</v>
+        <v>1209.514038085938</v>
       </c>
       <c r="C69" t="n">
-        <v>790.085693359375</v>
+        <v>790.0856323242188</v>
       </c>
       <c r="D69" t="n">
-        <v>1336.994506835938</v>
+        <v>1336.994384765625</v>
       </c>
     </row>
     <row r="70">
@@ -1413,13 +1413,13 @@
         <v>45180</v>
       </c>
       <c r="B70" t="n">
-        <v>1222.556884765625</v>
+        <v>1222.557006835938</v>
       </c>
       <c r="C70" t="n">
         <v>794.173828125</v>
       </c>
       <c r="D70" t="n">
-        <v>1343.226318359375</v>
+        <v>1343.226196289062</v>
       </c>
     </row>
     <row r="71">
@@ -1427,7 +1427,7 @@
         <v>45181</v>
       </c>
       <c r="B71" t="n">
-        <v>1204.894897460938</v>
+        <v>1204.89501953125</v>
       </c>
       <c r="C71" t="n">
         <v>796.6559448242188</v>
@@ -1441,13 +1441,13 @@
         <v>45182</v>
       </c>
       <c r="B72" t="n">
-        <v>1210.922119140625</v>
+        <v>1210.922241210938</v>
       </c>
       <c r="C72" t="n">
-        <v>800.062744140625</v>
+        <v>800.0626831054688</v>
       </c>
       <c r="D72" t="n">
-        <v>1363.150268554688</v>
+        <v>1363.150146484375</v>
       </c>
     </row>
     <row r="73">
@@ -1458,10 +1458,10 @@
         <v>1212.033813476562</v>
       </c>
       <c r="C73" t="n">
-        <v>799.5760498046875</v>
+        <v>799.5759887695312</v>
       </c>
       <c r="D73" t="n">
-        <v>1370.974243164062</v>
+        <v>1370.973999023438</v>
       </c>
     </row>
     <row r="74">
@@ -1472,10 +1472,10 @@
         <v>1214.28173828125</v>
       </c>
       <c r="C74" t="n">
-        <v>808.75</v>
+        <v>808.7500610351562</v>
       </c>
       <c r="D74" t="n">
-        <v>1375.204833984375</v>
+        <v>1375.204711914062</v>
       </c>
     </row>
     <row r="75">
@@ -1486,10 +1486,10 @@
         <v>1203.709228515625</v>
       </c>
       <c r="C75" t="n">
-        <v>792.8353881835938</v>
+        <v>792.83544921875</v>
       </c>
       <c r="D75" t="n">
-        <v>1357.19140625</v>
+        <v>1357.191284179688</v>
       </c>
     </row>
     <row r="76">
@@ -1503,7 +1503,7 @@
         <v>761.0304565429688</v>
       </c>
       <c r="D76" t="n">
-        <v>1355.781127929688</v>
+        <v>1355.78125</v>
       </c>
     </row>
     <row r="77">
@@ -1517,7 +1517,7 @@
         <v>755.9932861328125</v>
       </c>
       <c r="D77" t="n">
-        <v>1366.243408203125</v>
+        <v>1366.243530273438</v>
       </c>
     </row>
     <row r="78">
@@ -1545,7 +1545,7 @@
         <v>745.1158447265625</v>
       </c>
       <c r="D79" t="n">
-        <v>1341.133911132812</v>
+        <v>1341.1337890625</v>
       </c>
     </row>
     <row r="80">
@@ -1553,7 +1553,7 @@
         <v>45195</v>
       </c>
       <c r="B80" t="n">
-        <v>1157.2939453125</v>
+        <v>1157.293823242188</v>
       </c>
       <c r="C80" t="n">
         <v>748.3523559570312</v>
@@ -1567,13 +1567,13 @@
         <v>45196</v>
       </c>
       <c r="B81" t="n">
-        <v>1170.336669921875</v>
+        <v>1170.336547851562</v>
       </c>
       <c r="C81" t="n">
-        <v>743.0960693359375</v>
+        <v>743.0961303710938</v>
       </c>
       <c r="D81" t="n">
-        <v>1334.629150390625</v>
+        <v>1334.62890625</v>
       </c>
     </row>
     <row r="82">
@@ -1587,7 +1587,7 @@
         <v>741.5630493164062</v>
       </c>
       <c r="D82" t="n">
-        <v>1309.564819335938</v>
+        <v>1309.56494140625</v>
       </c>
     </row>
     <row r="83">
@@ -1601,7 +1601,7 @@
         <v>742.8284301757812</v>
       </c>
       <c r="D83" t="n">
-        <v>1305.926025390625</v>
+        <v>1305.92578125</v>
       </c>
     </row>
     <row r="84">
@@ -1612,10 +1612,10 @@
         <v>1145.263916015625</v>
       </c>
       <c r="C84" t="n">
-        <v>733.9464111328125</v>
+        <v>733.9464721679688</v>
       </c>
       <c r="D84" t="n">
-        <v>1304.606567382812</v>
+        <v>1304.606811523438</v>
       </c>
     </row>
     <row r="85">
@@ -1629,7 +1629,7 @@
         <v>744.4102172851562</v>
       </c>
       <c r="D85" t="n">
-        <v>1314.022827148438</v>
+        <v>1314.022705078125</v>
       </c>
     </row>
     <row r="86">
@@ -1637,13 +1637,13 @@
         <v>45204</v>
       </c>
       <c r="B86" t="n">
-        <v>1143.26318359375</v>
+        <v>1143.263061523438</v>
       </c>
       <c r="C86" t="n">
         <v>747.4276123046875</v>
       </c>
       <c r="D86" t="n">
-        <v>1331.3994140625</v>
+        <v>1331.399169921875</v>
       </c>
     </row>
     <row r="87">
@@ -1654,10 +1654,10 @@
         <v>1145.18994140625</v>
       </c>
       <c r="C87" t="n">
-        <v>746.600341796875</v>
+        <v>746.6002807617188</v>
       </c>
       <c r="D87" t="n">
-        <v>1345.273315429688</v>
+        <v>1345.273193359375</v>
       </c>
     </row>
     <row r="88">
@@ -1671,7 +1671,7 @@
         <v>737.937255859375</v>
       </c>
       <c r="D88" t="n">
-        <v>1342.31640625</v>
+        <v>1342.316528320312</v>
       </c>
     </row>
     <row r="89">
@@ -1682,10 +1682,10 @@
         <v>1140.447021484375</v>
       </c>
       <c r="C89" t="n">
-        <v>742.1227416992188</v>
+        <v>742.1226806640625</v>
       </c>
       <c r="D89" t="n">
-        <v>1360.239135742188</v>
+        <v>1360.239013671875</v>
       </c>
     </row>
     <row r="90">
@@ -1696,10 +1696,10 @@
         <v>1158.5537109375</v>
       </c>
       <c r="C90" t="n">
-        <v>749.3013305664062</v>
+        <v>749.3013916015625</v>
       </c>
       <c r="D90" t="n">
-        <v>1359.556762695312</v>
+        <v>1359.556640625</v>
       </c>
     </row>
     <row r="91">
@@ -1707,13 +1707,13 @@
         <v>45211</v>
       </c>
       <c r="B91" t="n">
-        <v>1160.702758789062</v>
+        <v>1160.70263671875</v>
       </c>
       <c r="C91" t="n">
         <v>754.2898559570312</v>
       </c>
       <c r="D91" t="n">
-        <v>1333.264526367188</v>
+        <v>1333.264282226562</v>
       </c>
     </row>
     <row r="92">
@@ -1727,7 +1727,7 @@
         <v>747.4276123046875</v>
       </c>
       <c r="D92" t="n">
-        <v>1302.013916015625</v>
+        <v>1302.013793945312</v>
       </c>
     </row>
     <row r="93">
@@ -1735,13 +1735,13 @@
         <v>45215</v>
       </c>
       <c r="B93" t="n">
-        <v>1158.059814453125</v>
+        <v>1158.059692382812</v>
       </c>
       <c r="C93" t="n">
         <v>744.4345092773438</v>
       </c>
       <c r="D93" t="n">
-        <v>1304.7431640625</v>
+        <v>1304.743286132812</v>
       </c>
     </row>
     <row r="94">
@@ -1755,7 +1755,7 @@
         <v>750.0800170898438</v>
       </c>
       <c r="D94" t="n">
-        <v>1312.294067382812</v>
+        <v>1312.294189453125</v>
       </c>
     </row>
     <row r="95">
@@ -1763,13 +1763,13 @@
         <v>45217</v>
       </c>
       <c r="B95" t="n">
-        <v>1148.154174804688</v>
+        <v>1148.154052734375</v>
       </c>
       <c r="C95" t="n">
-        <v>739.640625</v>
+        <v>739.6406860351562</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.565795898438</v>
+        <v>1310.565673828125</v>
       </c>
     </row>
     <row r="96">
@@ -1780,10 +1780,10 @@
         <v>1139.33544921875</v>
       </c>
       <c r="C96" t="n">
-        <v>737.3045654296875</v>
+        <v>737.3045043945312</v>
       </c>
       <c r="D96" t="n">
-        <v>1304.288452148438</v>
+        <v>1304.288208007812</v>
       </c>
     </row>
     <row r="97">
@@ -1797,7 +1797,7 @@
         <v>741.1250610351562</v>
       </c>
       <c r="D97" t="n">
-        <v>1298.4658203125</v>
+        <v>1298.465576171875</v>
       </c>
     </row>
     <row r="98">
@@ -1808,7 +1808,7 @@
         <v>1118.116333007812</v>
       </c>
       <c r="C98" t="n">
-        <v>732.9730224609375</v>
+        <v>732.9730834960938</v>
       </c>
       <c r="D98" t="n">
         <v>1281.544189453125</v>
@@ -1819,10 +1819,10 @@
         <v>45224</v>
       </c>
       <c r="B99" t="n">
-        <v>1115.522583007812</v>
+        <v>1115.522705078125</v>
       </c>
       <c r="C99" t="n">
-        <v>728.3252563476562</v>
+        <v>728.3251953125</v>
       </c>
       <c r="D99" t="n">
         <v>1262.560302734375</v>
@@ -1833,13 +1833,13 @@
         <v>45225</v>
       </c>
       <c r="B100" t="n">
-        <v>1099.984985351562</v>
+        <v>1099.985107421875</v>
       </c>
       <c r="C100" t="n">
         <v>712.2158813476562</v>
       </c>
       <c r="D100" t="n">
-        <v>1252.791870117188</v>
+        <v>1252.7919921875</v>
       </c>
     </row>
     <row r="101">
@@ -1853,7 +1853,7 @@
         <v>715.0143432617188</v>
       </c>
       <c r="D101" t="n">
-        <v>1272.052124023438</v>
+        <v>1272.05224609375</v>
       </c>
     </row>
     <row r="102">
@@ -1861,10 +1861,10 @@
         <v>45229</v>
       </c>
       <c r="B102" t="n">
-        <v>1142.47265625</v>
+        <v>1142.472534179688</v>
       </c>
       <c r="C102" t="n">
-        <v>722.7769775390625</v>
+        <v>722.7770385742188</v>
       </c>
       <c r="D102" t="n">
         <v>1269.011108398438</v>
@@ -1875,13 +1875,13 @@
         <v>45230</v>
       </c>
       <c r="B103" t="n">
-        <v>1130.319213867188</v>
+        <v>1130.319091796875</v>
       </c>
       <c r="C103" t="n">
-        <v>718.591552734375</v>
+        <v>718.5914916992188</v>
       </c>
       <c r="D103" t="n">
-        <v>1261.039794921875</v>
+        <v>1261.039672851562</v>
       </c>
     </row>
     <row r="104">
@@ -1895,7 +1895,7 @@
         <v>717.6181030273438</v>
       </c>
       <c r="D104" t="n">
-        <v>1247.90771484375</v>
+        <v>1247.907836914062</v>
       </c>
     </row>
     <row r="105">
@@ -1909,7 +1909,7 @@
         <v>718.7131958007812</v>
       </c>
       <c r="D105" t="n">
-        <v>1262.652465820312</v>
+        <v>1262.652587890625</v>
       </c>
     </row>
     <row r="106">
@@ -1920,7 +1920,7 @@
         <v>1146.029663085938</v>
       </c>
       <c r="C106" t="n">
-        <v>722.1199340820312</v>
+        <v>722.1199951171875</v>
       </c>
       <c r="D106" t="n">
         <v>1280.069580078125</v>
@@ -1934,10 +1934,10 @@
         <v>1155.564697265625</v>
       </c>
       <c r="C107" t="n">
-        <v>727.351806640625</v>
+        <v>727.3518676757812</v>
       </c>
       <c r="D107" t="n">
-        <v>1293.20166015625</v>
+        <v>1293.201782226562</v>
       </c>
     </row>
     <row r="108">
@@ -1965,7 +1965,7 @@
         <v>725.9161376953125</v>
       </c>
       <c r="D109" t="n">
-        <v>1281.866455078125</v>
+        <v>1281.866577148438</v>
       </c>
     </row>
     <row r="110">
@@ -1976,7 +1976,7 @@
         <v>1141.50927734375</v>
       </c>
       <c r="C110" t="n">
-        <v>723.044677734375</v>
+        <v>723.0447387695312</v>
       </c>
       <c r="D110" t="n">
         <v>1266.937622070312</v>
@@ -1987,13 +1987,13 @@
         <v>45240</v>
       </c>
       <c r="B111" t="n">
-        <v>1143.658325195312</v>
+        <v>1143.658203125</v>
       </c>
       <c r="C111" t="n">
-        <v>725.8917846679688</v>
+        <v>725.891845703125</v>
       </c>
       <c r="D111" t="n">
-        <v>1261.454467773438</v>
+        <v>1261.454345703125</v>
       </c>
     </row>
     <row r="112">
@@ -2001,10 +2001,10 @@
         <v>45243</v>
       </c>
       <c r="B112" t="n">
-        <v>1143.51025390625</v>
+        <v>1143.510131835938</v>
       </c>
       <c r="C112" t="n">
-        <v>724.5776977539062</v>
+        <v>724.5778198242188</v>
       </c>
       <c r="D112" t="n">
         <v>1265.78564453125</v>
@@ -2018,10 +2018,10 @@
         <v>1164.185791015625</v>
       </c>
       <c r="C113" t="n">
-        <v>732.1700439453125</v>
+        <v>732.1699829101562</v>
       </c>
       <c r="D113" t="n">
-        <v>1299.836791992188</v>
+        <v>1299.836669921875</v>
       </c>
     </row>
     <row r="114">
@@ -2035,7 +2035,7 @@
         <v>734.0924072265625</v>
       </c>
       <c r="D114" t="n">
-        <v>1331.537841796875</v>
+        <v>1331.537719726562</v>
       </c>
     </row>
     <row r="115">
@@ -2063,7 +2063,7 @@
         <v>732.559326171875</v>
       </c>
       <c r="D116" t="n">
-        <v>1323.888916015625</v>
+        <v>1323.889038085938</v>
       </c>
     </row>
     <row r="117">
@@ -2074,7 +2074,7 @@
         <v>1175.276977539062</v>
       </c>
       <c r="C117" t="n">
-        <v>738.7645874023438</v>
+        <v>738.7646484375</v>
       </c>
       <c r="D117" t="n">
         <v>1326.100708007812</v>
@@ -2088,10 +2088,10 @@
         <v>1179.87158203125</v>
       </c>
       <c r="C118" t="n">
-        <v>736.1365356445312</v>
+        <v>736.1365966796875</v>
       </c>
       <c r="D118" t="n">
-        <v>1343.425903320312</v>
+        <v>1343.425659179688</v>
       </c>
     </row>
     <row r="119">
@@ -2119,7 +2119,7 @@
         <v>745.6511840820312</v>
       </c>
       <c r="D120" t="n">
-        <v>1324.626098632812</v>
+        <v>1324.626342773438</v>
       </c>
     </row>
     <row r="121">
@@ -2133,7 +2133,7 @@
         <v>743.97216796875</v>
       </c>
       <c r="D121" t="n">
-        <v>1329.510498046875</v>
+        <v>1329.51025390625</v>
       </c>
     </row>
     <row r="122">
@@ -2158,10 +2158,10 @@
         <v>1174.560668945312</v>
       </c>
       <c r="C123" t="n">
-        <v>758.6456909179688</v>
+        <v>758.645751953125</v>
       </c>
       <c r="D123" t="n">
-        <v>1340.983520507812</v>
+        <v>1340.983642578125</v>
       </c>
     </row>
     <row r="124">
@@ -2169,10 +2169,10 @@
         <v>45261</v>
       </c>
       <c r="B124" t="n">
-        <v>1182.885375976562</v>
+        <v>1182.88525390625</v>
       </c>
       <c r="C124" t="n">
-        <v>756.990966796875</v>
+        <v>756.9910278320312</v>
       </c>
       <c r="D124" t="n">
         <v>1338.357299804688</v>
@@ -2183,13 +2183,13 @@
         <v>45264</v>
       </c>
       <c r="B125" t="n">
-        <v>1195.681030273438</v>
+        <v>1195.680908203125</v>
       </c>
       <c r="C125" t="n">
         <v>783.2720336914062</v>
       </c>
       <c r="D125" t="n">
-        <v>1349.461791992188</v>
+        <v>1349.461669921875</v>
       </c>
     </row>
     <row r="126">
@@ -2200,7 +2200,7 @@
         <v>1204.351440429688</v>
       </c>
       <c r="C126" t="n">
-        <v>790.2316284179688</v>
+        <v>790.2315673828125</v>
       </c>
       <c r="D126" t="n">
         <v>1339.877685546875</v>
@@ -2211,7 +2211,7 @@
         <v>45266</v>
       </c>
       <c r="B127" t="n">
-        <v>1215.887451171875</v>
+        <v>1215.887329101562</v>
       </c>
       <c r="C127" t="n">
         <v>792.22705078125</v>
@@ -2231,7 +2231,7 @@
         <v>793.5167236328125</v>
       </c>
       <c r="D128" t="n">
-        <v>1350.890258789062</v>
+        <v>1350.89013671875</v>
       </c>
     </row>
     <row r="129">
@@ -2239,13 +2239,13 @@
         <v>45268</v>
       </c>
       <c r="B129" t="n">
-        <v>1213.244140625</v>
+        <v>1213.244262695312</v>
       </c>
       <c r="C129" t="n">
-        <v>804.5888671875</v>
+        <v>804.5888061523438</v>
       </c>
       <c r="D129" t="n">
-        <v>1374.1591796875</v>
+        <v>1374.159301757812</v>
       </c>
     </row>
     <row r="130">
@@ -2256,10 +2256,10 @@
         <v>1215.022705078125</v>
       </c>
       <c r="C130" t="n">
-        <v>803.5181884765625</v>
+        <v>803.5181274414062</v>
       </c>
       <c r="D130" t="n">
-        <v>1371.717163085938</v>
+        <v>1371.716918945312</v>
       </c>
     </row>
     <row r="131">
@@ -2267,13 +2267,13 @@
         <v>45272</v>
       </c>
       <c r="B131" t="n">
-        <v>1197.5830078125</v>
+        <v>1197.583129882812</v>
       </c>
       <c r="C131" t="n">
         <v>795.5364990234375</v>
       </c>
       <c r="D131" t="n">
-        <v>1360.243896484375</v>
+        <v>1360.244018554688</v>
       </c>
     </row>
     <row r="132">
@@ -2287,7 +2287,7 @@
         <v>793.7357788085938</v>
       </c>
       <c r="D132" t="n">
-        <v>1335.316162109375</v>
+        <v>1335.316040039062</v>
       </c>
     </row>
     <row r="133">
@@ -2301,7 +2301,7 @@
         <v>803.1044921875</v>
       </c>
       <c r="D133" t="n">
-        <v>1383.651123046875</v>
+        <v>1383.651000976562</v>
       </c>
     </row>
     <row r="134">
@@ -2312,10 +2312,10 @@
         <v>1232.931762695312</v>
       </c>
       <c r="C134" t="n">
-        <v>806.2192993164062</v>
+        <v>806.21923828125</v>
       </c>
       <c r="D134" t="n">
-        <v>1454.563842773438</v>
+        <v>1454.563720703125</v>
       </c>
     </row>
     <row r="135">
@@ -2326,10 +2326,10 @@
         <v>1245.480346679688</v>
       </c>
       <c r="C135" t="n">
-        <v>805.8056030273438</v>
+        <v>805.8055419921875</v>
       </c>
       <c r="D135" t="n">
-        <v>1441.6162109375</v>
+        <v>1441.615966796875</v>
       </c>
     </row>
     <row r="136">
@@ -2340,7 +2340,7 @@
         <v>1263.809448242188</v>
       </c>
       <c r="C136" t="n">
-        <v>804.4428100585938</v>
+        <v>804.44287109375</v>
       </c>
       <c r="D136" t="n">
         <v>1436.040771484375</v>
@@ -2354,7 +2354,7 @@
         <v>1248.518798828125</v>
       </c>
       <c r="C137" t="n">
-        <v>806.4382934570312</v>
+        <v>806.438232421875</v>
       </c>
       <c r="D137" t="n">
         <v>1415.859008789062</v>
@@ -2365,13 +2365,13 @@
         <v>45281</v>
       </c>
       <c r="B138" t="n">
-        <v>1266.008056640625</v>
+        <v>1266.007934570312</v>
       </c>
       <c r="C138" t="n">
-        <v>820.8927612304688</v>
+        <v>820.892822265625</v>
       </c>
       <c r="D138" t="n">
-        <v>1415.490356445312</v>
+        <v>1415.490478515625</v>
       </c>
     </row>
     <row r="139">
@@ -2379,13 +2379,13 @@
         <v>45282</v>
       </c>
       <c r="B139" t="n">
-        <v>1267.243041992188</v>
+        <v>1267.242919921875</v>
       </c>
       <c r="C139" t="n">
-        <v>813.1788330078125</v>
+        <v>813.1788940429688</v>
       </c>
       <c r="D139" t="n">
-        <v>1440.27978515625</v>
+        <v>1440.280029296875</v>
       </c>
     </row>
     <row r="140">
@@ -2399,7 +2399,7 @@
         <v>818.8244018554688</v>
       </c>
       <c r="D140" t="n">
-        <v>1422.816528320312</v>
+        <v>1422.816650390625</v>
       </c>
     </row>
     <row r="141">
@@ -2410,7 +2410,7 @@
         <v>1278.01318359375</v>
       </c>
       <c r="C141" t="n">
-        <v>828.9718627929688</v>
+        <v>828.9718017578125</v>
       </c>
       <c r="D141" t="n">
         <v>1444.150268554688</v>
@@ -2421,13 +2421,13 @@
         <v>45288</v>
       </c>
       <c r="B142" t="n">
-        <v>1287.251831054688</v>
+        <v>1287.251708984375</v>
       </c>
       <c r="C142" t="n">
         <v>829.9208374023438</v>
       </c>
       <c r="D142" t="n">
-        <v>1440.049560546875</v>
+        <v>1440.049438476562</v>
       </c>
     </row>
     <row r="143">
@@ -2438,7 +2438,7 @@
         <v>1277.074462890625</v>
       </c>
       <c r="C143" t="n">
-        <v>831.8675537109375</v>
+        <v>831.8676147460938</v>
       </c>
       <c r="D143" t="n">
         <v>1421.848999023438</v>
@@ -2466,10 +2466,10 @@
         <v>1290.2900390625</v>
       </c>
       <c r="C145" t="n">
-        <v>826.9276733398438</v>
+        <v>826.927734375</v>
       </c>
       <c r="D145" t="n">
-        <v>1414.015869140625</v>
+        <v>1414.015747070312</v>
       </c>
     </row>
     <row r="146">
@@ -2477,13 +2477,13 @@
         <v>45294</v>
       </c>
       <c r="B146" t="n">
-        <v>1276.25927734375</v>
+        <v>1276.259399414062</v>
       </c>
       <c r="C146" t="n">
-        <v>814.176513671875</v>
+        <v>814.1766357421875</v>
       </c>
       <c r="D146" t="n">
-        <v>1373.099365234375</v>
+        <v>1373.099487304688</v>
       </c>
     </row>
     <row r="147">
@@ -2491,13 +2491,13 @@
         <v>45295</v>
       </c>
       <c r="B147" t="n">
-        <v>1282.854736328125</v>
+        <v>1282.854614257812</v>
       </c>
       <c r="C147" t="n">
-        <v>822.9125366210938</v>
+        <v>822.91259765625</v>
       </c>
       <c r="D147" t="n">
-        <v>1394.018310546875</v>
+        <v>1394.018432617188</v>
       </c>
     </row>
     <row r="148">
@@ -2508,10 +2508,10 @@
         <v>1288.313842773438</v>
       </c>
       <c r="C148" t="n">
-        <v>818.7026977539062</v>
+        <v>818.7027587890625</v>
       </c>
       <c r="D148" t="n">
-        <v>1412.31103515625</v>
+        <v>1412.311157226562</v>
       </c>
     </row>
     <row r="149">
@@ -2525,7 +2525,7 @@
         <v>809.577392578125</v>
       </c>
       <c r="D149" t="n">
-        <v>1403.325927734375</v>
+        <v>1403.326049804688</v>
       </c>
     </row>
     <row r="150">
@@ -2533,7 +2533,7 @@
         <v>45300</v>
       </c>
       <c r="B150" t="n">
-        <v>1274.8759765625</v>
+        <v>1274.875854492188</v>
       </c>
       <c r="C150" t="n">
         <v>803.2747802734375</v>
@@ -2547,7 +2547,7 @@
         <v>45301</v>
       </c>
       <c r="B151" t="n">
-        <v>1309.261474609375</v>
+        <v>1309.26123046875</v>
       </c>
       <c r="C151" t="n">
         <v>805.92724609375</v>
@@ -2561,7 +2561,7 @@
         <v>45302</v>
       </c>
       <c r="B152" t="n">
-        <v>1343.696044921875</v>
+        <v>1343.696166992188</v>
       </c>
       <c r="C152" t="n">
         <v>802.5447998046875</v>
@@ -2575,10 +2575,10 @@
         <v>45303</v>
       </c>
       <c r="B153" t="n">
-        <v>1354.39208984375</v>
+        <v>1354.391967773438</v>
       </c>
       <c r="C153" t="n">
-        <v>798.7485961914062</v>
+        <v>798.74853515625</v>
       </c>
       <c r="D153" t="n">
         <v>1486.21875</v>
@@ -2592,10 +2592,10 @@
         <v>1377.51318359375</v>
       </c>
       <c r="C154" t="n">
-        <v>814.1278686523438</v>
+        <v>814.1279907226562</v>
       </c>
       <c r="D154" t="n">
-        <v>1522.481567382812</v>
+        <v>1522.4814453125</v>
       </c>
     </row>
     <row r="155">
@@ -2606,10 +2606,10 @@
         <v>1358.24560546875</v>
       </c>
       <c r="C155" t="n">
-        <v>817.2183227539062</v>
+        <v>817.2183837890625</v>
       </c>
       <c r="D155" t="n">
-        <v>1503.543823242188</v>
+        <v>1503.5439453125</v>
       </c>
     </row>
     <row r="156">
@@ -2617,13 +2617,13 @@
         <v>45308</v>
       </c>
       <c r="B156" t="n">
-        <v>1345.350952148438</v>
+        <v>1345.35107421875</v>
       </c>
       <c r="C156" t="n">
         <v>748.279296875</v>
       </c>
       <c r="D156" t="n">
-        <v>1511.515014648438</v>
+        <v>1511.51513671875</v>
       </c>
     </row>
     <row r="157">
@@ -2631,13 +2631,13 @@
         <v>45309</v>
       </c>
       <c r="B157" t="n">
-        <v>1351.650146484375</v>
+        <v>1351.650024414062</v>
       </c>
       <c r="C157" t="n">
-        <v>723.2880249023438</v>
+        <v>723.2879638671875</v>
       </c>
       <c r="D157" t="n">
-        <v>1513.726806640625</v>
+        <v>1513.726928710938</v>
       </c>
     </row>
     <row r="158">
@@ -2645,7 +2645,7 @@
         <v>45310</v>
       </c>
       <c r="B158" t="n">
-        <v>1351.156127929688</v>
+        <v>1351.156005859375</v>
       </c>
       <c r="C158" t="n">
         <v>715.744384765625</v>
@@ -2665,7 +2665,7 @@
         <v>694.6708984375</v>
       </c>
       <c r="D159" t="n">
-        <v>1513.31201171875</v>
+        <v>1513.312255859375</v>
       </c>
     </row>
     <row r="160">
@@ -2673,7 +2673,7 @@
         <v>45315</v>
       </c>
       <c r="B160" t="n">
-        <v>1327.861938476562</v>
+        <v>1327.862060546875</v>
       </c>
       <c r="C160" t="n">
         <v>708.5657958984375</v>
@@ -2687,13 +2687,13 @@
         <v>45316</v>
       </c>
       <c r="B161" t="n">
-        <v>1336.952392578125</v>
+        <v>1336.952270507812</v>
       </c>
       <c r="C161" t="n">
         <v>698.3453979492188</v>
       </c>
       <c r="D161" t="n">
-        <v>1538.147705078125</v>
+        <v>1538.147827148438</v>
       </c>
     </row>
     <row r="162">
@@ -2701,13 +2701,13 @@
         <v>45320</v>
       </c>
       <c r="B162" t="n">
-        <v>1430.795654296875</v>
+        <v>1430.795776367188</v>
       </c>
       <c r="C162" t="n">
         <v>707.9573974609375</v>
       </c>
       <c r="D162" t="n">
-        <v>1526.62841796875</v>
+        <v>1526.628540039062</v>
       </c>
     </row>
     <row r="163">
@@ -2729,7 +2729,7 @@
         <v>45322</v>
       </c>
       <c r="B164" t="n">
-        <v>1409.6259765625</v>
+        <v>1409.625854492188</v>
       </c>
       <c r="C164" t="n">
         <v>711.80224609375</v>
@@ -2749,7 +2749,7 @@
         <v>713.651611328125</v>
       </c>
       <c r="D165" t="n">
-        <v>1527.043212890625</v>
+        <v>1527.043334960938</v>
       </c>
     </row>
     <row r="166">
@@ -2757,13 +2757,13 @@
         <v>45324</v>
       </c>
       <c r="B166" t="n">
-        <v>1440.33056640625</v>
+        <v>1440.330688476562</v>
       </c>
       <c r="C166" t="n">
         <v>703.8206176757812</v>
       </c>
       <c r="D166" t="n">
-        <v>1560.495239257812</v>
+        <v>1560.4951171875</v>
       </c>
     </row>
     <row r="167">
@@ -2774,10 +2774,10 @@
         <v>1421.878173828125</v>
       </c>
       <c r="C167" t="n">
-        <v>703.1879272460938</v>
+        <v>703.1878662109375</v>
       </c>
       <c r="D167" t="n">
-        <v>1554.827758789062</v>
+        <v>1554.82763671875</v>
       </c>
     </row>
     <row r="168">
@@ -2791,7 +2791,7 @@
         <v>702.8228759765625</v>
       </c>
       <c r="D168" t="n">
-        <v>1593.762817382812</v>
+        <v>1593.762939453125</v>
       </c>
     </row>
     <row r="169">
@@ -2799,13 +2799,13 @@
         <v>45329</v>
       </c>
       <c r="B169" t="n">
-        <v>1424.966064453125</v>
+        <v>1424.965942382812</v>
       </c>
       <c r="C169" t="n">
         <v>695.9362182617188</v>
       </c>
       <c r="D169" t="n">
-        <v>1560.863891601562</v>
+        <v>1560.86376953125</v>
       </c>
     </row>
     <row r="170">
@@ -2819,7 +2819,7 @@
         <v>682.8444213867188</v>
       </c>
       <c r="D170" t="n">
-        <v>1559.343139648438</v>
+        <v>1559.34326171875</v>
       </c>
     </row>
     <row r="171">
@@ -2833,7 +2833,7 @@
         <v>683.112060546875</v>
       </c>
       <c r="D171" t="n">
-        <v>1538.378295898438</v>
+        <v>1538.378173828125</v>
       </c>
     </row>
     <row r="172">
@@ -2844,10 +2844,10 @@
         <v>1435.04443359375</v>
       </c>
       <c r="C172" t="n">
-        <v>676.4931640625</v>
+        <v>676.4932250976562</v>
       </c>
       <c r="D172" t="n">
-        <v>1548.28466796875</v>
+        <v>1548.284912109375</v>
       </c>
     </row>
     <row r="173">
@@ -2855,10 +2855,10 @@
         <v>45335</v>
       </c>
       <c r="B173" t="n">
-        <v>1447.642456054688</v>
+        <v>1447.642333984375</v>
       </c>
       <c r="C173" t="n">
-        <v>678.658935546875</v>
+        <v>678.6588745117188</v>
       </c>
       <c r="D173" t="n">
         <v>1552.385620117188</v>
@@ -2869,10 +2869,10 @@
         <v>45336</v>
       </c>
       <c r="B174" t="n">
-        <v>1463.7236328125</v>
+        <v>1463.723510742188</v>
       </c>
       <c r="C174" t="n">
-        <v>673.597412109375</v>
+        <v>673.5974731445312</v>
       </c>
       <c r="D174" t="n">
         <v>1535.475341796875</v>
@@ -2889,7 +2889,7 @@
         <v>688.197998046875</v>
       </c>
       <c r="D175" t="n">
-        <v>1544.828857421875</v>
+        <v>1544.828979492188</v>
       </c>
     </row>
     <row r="176">
@@ -2897,7 +2897,7 @@
         <v>45338</v>
       </c>
       <c r="B176" t="n">
-        <v>1443.171264648438</v>
+        <v>1443.17138671875</v>
       </c>
       <c r="C176" t="n">
         <v>691.0451049804688</v>
@@ -2917,7 +2917,7 @@
         <v>689.682373046875</v>
       </c>
       <c r="D177" t="n">
-        <v>1566.39306640625</v>
+        <v>1566.393188476562</v>
       </c>
     </row>
     <row r="178">
@@ -2931,7 +2931,7 @@
         <v>707.7870483398438</v>
       </c>
       <c r="D178" t="n">
-        <v>1553.030883789062</v>
+        <v>1553.030517578125</v>
       </c>
     </row>
     <row r="179">
@@ -2942,7 +2942,7 @@
         <v>1450.211547851562</v>
       </c>
       <c r="C179" t="n">
-        <v>700.413818359375</v>
+        <v>700.4137573242188</v>
       </c>
       <c r="D179" t="n">
         <v>1525.660888671875</v>
@@ -2970,7 +2970,7 @@
         <v>1475.82763671875</v>
       </c>
       <c r="C181" t="n">
-        <v>691.3858032226562</v>
+        <v>691.3857421875</v>
       </c>
       <c r="D181" t="n">
         <v>1545.289672851562</v>
@@ -2981,13 +2981,13 @@
         <v>45348</v>
       </c>
       <c r="B182" t="n">
-        <v>1469.6025390625</v>
+        <v>1469.602661132812</v>
       </c>
       <c r="C182" t="n">
-        <v>692.213134765625</v>
+        <v>692.2131958007812</v>
       </c>
       <c r="D182" t="n">
-        <v>1529.89990234375</v>
+        <v>1529.900024414062</v>
       </c>
     </row>
     <row r="183">
@@ -2995,7 +2995,7 @@
         <v>45349</v>
       </c>
       <c r="B183" t="n">
-        <v>1467.947631835938</v>
+        <v>1467.94775390625</v>
       </c>
       <c r="C183" t="n">
         <v>691.1668090820312</v>
@@ -3009,13 +3009,13 @@
         <v>45350</v>
       </c>
       <c r="B184" t="n">
-        <v>1438.2802734375</v>
+        <v>1438.280395507812</v>
       </c>
       <c r="C184" t="n">
         <v>685.9348754882812</v>
       </c>
       <c r="D184" t="n">
-        <v>1540.129028320312</v>
+        <v>1540.129150390625</v>
       </c>
     </row>
     <row r="185">
@@ -3023,13 +3023,13 @@
         <v>45351</v>
       </c>
       <c r="B185" t="n">
-        <v>1443.393798828125</v>
+        <v>1443.393920898438</v>
       </c>
       <c r="C185" t="n">
         <v>683.0147705078125</v>
       </c>
       <c r="D185" t="n">
-        <v>1542.5712890625</v>
+        <v>1542.571166992188</v>
       </c>
     </row>
     <row r="186">
@@ -3043,7 +3043,7 @@
         <v>696.3256225585938</v>
       </c>
       <c r="D186" t="n">
-        <v>1524.877563476562</v>
+        <v>1524.87744140625</v>
       </c>
     </row>
     <row r="187">
@@ -3054,10 +3054,10 @@
         <v>1489.4384765625</v>
       </c>
       <c r="C187" t="n">
-        <v>697.274658203125</v>
+        <v>697.2745971679688</v>
       </c>
       <c r="D187" t="n">
-        <v>1508.75048828125</v>
+        <v>1508.750610351562</v>
       </c>
     </row>
     <row r="188">
@@ -3068,7 +3068,7 @@
         <v>1482.32421875</v>
       </c>
       <c r="C188" t="n">
-        <v>701.2410888671875</v>
+        <v>701.2411499023438</v>
       </c>
       <c r="D188" t="n">
         <v>1480.459228515625</v>
@@ -3079,10 +3079,10 @@
         <v>45357</v>
       </c>
       <c r="B189" t="n">
-        <v>1485.090942382812</v>
+        <v>1485.0908203125</v>
       </c>
       <c r="C189" t="n">
-        <v>702.0927734375</v>
+        <v>702.0928344726562</v>
       </c>
       <c r="D189" t="n">
         <v>1490.642333984375</v>
@@ -3107,7 +3107,7 @@
         <v>45362</v>
       </c>
       <c r="B191" t="n">
-        <v>1449.12451171875</v>
+        <v>1449.124633789062</v>
       </c>
       <c r="C191" t="n">
         <v>694.8899536132812</v>
@@ -3121,13 +3121,13 @@
         <v>45363</v>
       </c>
       <c r="B192" t="n">
-        <v>1457.844482421875</v>
+        <v>1457.844604492188</v>
       </c>
       <c r="C192" t="n">
-        <v>710.3422241210938</v>
+        <v>710.3421630859375</v>
       </c>
       <c r="D192" t="n">
-        <v>1486.403198242188</v>
+        <v>1486.403076171875</v>
       </c>
     </row>
     <row r="193">
@@ -3149,13 +3149,13 @@
         <v>45365</v>
       </c>
       <c r="B194" t="n">
-        <v>1414.418212890625</v>
+        <v>1414.418090820312</v>
       </c>
       <c r="C194" t="n">
         <v>708.3467407226562</v>
       </c>
       <c r="D194" t="n">
-        <v>1523.58740234375</v>
+        <v>1523.587524414062</v>
       </c>
     </row>
     <row r="195">
@@ -3177,13 +3177,13 @@
         <v>45369</v>
       </c>
       <c r="B196" t="n">
-        <v>1422.32275390625</v>
+        <v>1422.322875976562</v>
       </c>
       <c r="C196" t="n">
         <v>703.77197265625</v>
       </c>
       <c r="D196" t="n">
-        <v>1476.911376953125</v>
+        <v>1476.911254882812</v>
       </c>
     </row>
     <row r="197">
@@ -3194,10 +3194,10 @@
         <v>1408.267333984375</v>
       </c>
       <c r="C197" t="n">
-        <v>705.3779907226562</v>
+        <v>705.3779296875</v>
       </c>
       <c r="D197" t="n">
-        <v>1438.943603515625</v>
+        <v>1438.943725585938</v>
       </c>
     </row>
     <row r="198">
@@ -3208,10 +3208,10 @@
         <v>1426.546875</v>
       </c>
       <c r="C198" t="n">
-        <v>696.4716186523438</v>
+        <v>696.4716796875</v>
       </c>
       <c r="D198" t="n">
-        <v>1432.953491210938</v>
+        <v>1432.95361328125</v>
       </c>
     </row>
     <row r="199">
@@ -3239,7 +3239,7 @@
         <v>702.2144775390625</v>
       </c>
       <c r="D200" t="n">
-        <v>1390.470581054688</v>
+        <v>1390.470336914062</v>
       </c>
     </row>
     <row r="201">
@@ -3247,7 +3247,7 @@
         <v>45377</v>
       </c>
       <c r="B201" t="n">
-        <v>1424.397705078125</v>
+        <v>1424.397827148438</v>
       </c>
       <c r="C201" t="n">
         <v>693.7218627929688</v>
@@ -3261,13 +3261,13 @@
         <v>45378</v>
       </c>
       <c r="B202" t="n">
-        <v>1475.061889648438</v>
+        <v>1475.061767578125</v>
       </c>
       <c r="C202" t="n">
         <v>701.1681518554688</v>
       </c>
       <c r="D202" t="n">
-        <v>1367.431884765625</v>
+        <v>1367.431762695312</v>
       </c>
     </row>
     <row r="203">
@@ -3275,13 +3275,13 @@
         <v>45379</v>
       </c>
       <c r="B203" t="n">
-        <v>1468.145263671875</v>
+        <v>1468.145141601562</v>
       </c>
       <c r="C203" t="n">
-        <v>704.6723022460938</v>
+        <v>704.6722412109375</v>
       </c>
       <c r="D203" t="n">
-        <v>1380.517944335938</v>
+        <v>1380.517822265625</v>
       </c>
     </row>
     <row r="204">
@@ -3289,13 +3289,13 @@
         <v>45383</v>
       </c>
       <c r="B204" t="n">
-        <v>1467.083129882812</v>
+        <v>1467.0830078125</v>
       </c>
       <c r="C204" t="n">
         <v>715.67138671875</v>
       </c>
       <c r="D204" t="n">
-        <v>1378.121704101562</v>
+        <v>1378.121826171875</v>
       </c>
     </row>
     <row r="205">
@@ -3306,10 +3306,10 @@
         <v>1469.232055664062</v>
       </c>
       <c r="C205" t="n">
-        <v>720.3678588867188</v>
+        <v>720.367919921875</v>
       </c>
       <c r="D205" t="n">
-        <v>1366.51025390625</v>
+        <v>1366.510375976562</v>
       </c>
     </row>
     <row r="206">
@@ -3323,7 +3323,7 @@
         <v>721.414306640625</v>
       </c>
       <c r="D206" t="n">
-        <v>1364.483032226562</v>
+        <v>1364.48291015625</v>
       </c>
     </row>
     <row r="207">
@@ -3337,7 +3337,7 @@
         <v>743.461181640625</v>
       </c>
       <c r="D207" t="n">
-        <v>1370.058349609375</v>
+        <v>1370.058227539062</v>
       </c>
     </row>
     <row r="208">
@@ -3351,7 +3351,7 @@
         <v>754.1439208984375</v>
       </c>
       <c r="D208" t="n">
-        <v>1363.054565429688</v>
+        <v>1363.054443359375</v>
       </c>
     </row>
     <row r="209">
@@ -3362,10 +3362,10 @@
         <v>1468.268676757812</v>
       </c>
       <c r="C209" t="n">
-        <v>752.7081909179688</v>
+        <v>752.7081298828125</v>
       </c>
       <c r="D209" t="n">
-        <v>1360.8427734375</v>
+        <v>1360.842895507812</v>
       </c>
     </row>
     <row r="210">
@@ -3376,10 +3376,10 @@
         <v>1446.209838867188</v>
       </c>
       <c r="C210" t="n">
-        <v>753.6572265625</v>
+        <v>753.6572875976562</v>
       </c>
       <c r="D210" t="n">
-        <v>1377.568725585938</v>
+        <v>1377.56884765625</v>
       </c>
     </row>
     <row r="211">
@@ -3418,7 +3418,7 @@
         <v>1447.370727539062</v>
       </c>
       <c r="C213" t="n">
-        <v>727.4490966796875</v>
+        <v>727.4491577148438</v>
       </c>
       <c r="D213" t="n">
         <v>1352.963745117188</v>
@@ -3446,7 +3446,7 @@
         <v>1446.876708984375</v>
       </c>
       <c r="C215" t="n">
-        <v>727.4490966796875</v>
+        <v>727.4491577148438</v>
       </c>
       <c r="D215" t="n">
         <v>1307.900268554688</v>
@@ -3457,7 +3457,7 @@
         <v>45401</v>
       </c>
       <c r="B216" t="n">
-        <v>1452.607788085938</v>
+        <v>1452.607666015625</v>
       </c>
       <c r="C216" t="n">
         <v>745.2619018554688</v>
@@ -3474,10 +3474,10 @@
         <v>1462.216674804688</v>
       </c>
       <c r="C217" t="n">
-        <v>735.9661254882812</v>
+        <v>735.9661865234375</v>
       </c>
       <c r="D217" t="n">
-        <v>1320.340942382812</v>
+        <v>1320.341064453125</v>
       </c>
     </row>
     <row r="218">
@@ -3488,10 +3488,10 @@
         <v>1441.936279296875</v>
       </c>
       <c r="C218" t="n">
-        <v>733.7273559570312</v>
+        <v>733.7274169921875</v>
       </c>
       <c r="D218" t="n">
-        <v>1329.234008789062</v>
+        <v>1329.23388671875</v>
       </c>
     </row>
     <row r="219">
@@ -3499,13 +3499,13 @@
         <v>45406</v>
       </c>
       <c r="B219" t="n">
-        <v>1432.895263671875</v>
+        <v>1432.895385742188</v>
       </c>
       <c r="C219" t="n">
-        <v>735.7228393554688</v>
+        <v>735.7227783203125</v>
       </c>
       <c r="D219" t="n">
-        <v>1318.497802734375</v>
+        <v>1318.497924804688</v>
       </c>
     </row>
     <row r="220">
@@ -3513,13 +3513,13 @@
         <v>45407</v>
       </c>
       <c r="B220" t="n">
-        <v>1442.57861328125</v>
+        <v>1442.578491210938</v>
       </c>
       <c r="C220" t="n">
         <v>735.260498046875</v>
       </c>
       <c r="D220" t="n">
-        <v>1325.59375</v>
+        <v>1325.593627929688</v>
       </c>
     </row>
     <row r="221">
@@ -3527,7 +3527,7 @@
         <v>45408</v>
       </c>
       <c r="B221" t="n">
-        <v>1435.2421875</v>
+        <v>1435.242065429688</v>
       </c>
       <c r="C221" t="n">
         <v>734.7981567382812</v>
@@ -3541,7 +3541,7 @@
         <v>45411</v>
       </c>
       <c r="B222" t="n">
-        <v>1447.568359375</v>
+        <v>1447.568481445312</v>
       </c>
       <c r="C222" t="n">
         <v>744.3858642578125</v>
@@ -3572,7 +3572,7 @@
         <v>1449.075317382812</v>
       </c>
       <c r="C224" t="n">
-        <v>745.7241821289062</v>
+        <v>745.7242431640625</v>
       </c>
       <c r="D224" t="n">
         <v>1303.476684570312</v>
@@ -3589,7 +3589,7 @@
         <v>739.567626953125</v>
       </c>
       <c r="D225" t="n">
-        <v>1305.181762695312</v>
+        <v>1305.181640625</v>
       </c>
     </row>
     <row r="226">
@@ -3603,7 +3603,7 @@
         <v>741.0520629882812</v>
       </c>
       <c r="D226" t="n">
-        <v>1314.028564453125</v>
+        <v>1314.028442382812</v>
       </c>
     </row>
     <row r="227">
@@ -3617,7 +3617,7 @@
         <v>733.021728515625</v>
       </c>
       <c r="D227" t="n">
-        <v>1327.8974609375</v>
+        <v>1327.897583007812</v>
       </c>
     </row>
     <row r="228">
@@ -3625,13 +3625,13 @@
         <v>45420</v>
       </c>
       <c r="B228" t="n">
-        <v>1401.647338867188</v>
+        <v>1401.647094726562</v>
       </c>
       <c r="C228" t="n">
         <v>721.5845947265625</v>
       </c>
       <c r="D228" t="n">
-        <v>1315.318603515625</v>
+        <v>1315.318725585938</v>
       </c>
     </row>
     <row r="229">
@@ -3645,7 +3645,7 @@
         <v>704.4776000976562</v>
       </c>
       <c r="D229" t="n">
-        <v>1326.607421875</v>
+        <v>1326.607543945312</v>
       </c>
     </row>
     <row r="230">
@@ -3656,10 +3656,10 @@
         <v>1390.65478515625</v>
       </c>
       <c r="C230" t="n">
-        <v>709.361572265625</v>
+        <v>709.3616333007812</v>
       </c>
       <c r="D230" t="n">
-        <v>1313.10693359375</v>
+        <v>1313.106811523438</v>
       </c>
     </row>
     <row r="231">
@@ -3667,13 +3667,13 @@
         <v>45425</v>
       </c>
       <c r="B231" t="n">
-        <v>1385.985961914062</v>
+        <v>1385.986083984375</v>
       </c>
       <c r="C231" t="n">
         <v>717.9208984375</v>
       </c>
       <c r="D231" t="n">
-        <v>1311.770629882812</v>
+        <v>1311.7705078125</v>
       </c>
     </row>
     <row r="232">
@@ -3687,7 +3687,7 @@
         <v>720.7328491210938</v>
       </c>
       <c r="D232" t="n">
-        <v>1312.922607421875</v>
+        <v>1312.922485351562</v>
       </c>
     </row>
     <row r="233">
@@ -3695,13 +3695,13 @@
         <v>45427</v>
       </c>
       <c r="B233" t="n">
-        <v>1399.399291992188</v>
+        <v>1399.3994140625</v>
       </c>
       <c r="C233" t="n">
-        <v>709.6575927734375</v>
+        <v>709.6575317382812</v>
       </c>
       <c r="D233" t="n">
-        <v>1308.545166015625</v>
+        <v>1308.545288085938</v>
       </c>
     </row>
     <row r="234">
@@ -3737,13 +3737,13 @@
         <v>45433</v>
       </c>
       <c r="B236" t="n">
-        <v>1419.012817382812</v>
+        <v>1419.0126953125</v>
       </c>
       <c r="C236" t="n">
-        <v>719.6721801757812</v>
+        <v>719.6722412109375</v>
       </c>
       <c r="D236" t="n">
-        <v>1321.631225585938</v>
+        <v>1321.631103515625</v>
       </c>
     </row>
     <row r="237">
@@ -3751,10 +3751,10 @@
         <v>45434</v>
       </c>
       <c r="B237" t="n">
-        <v>1443.24560546875</v>
+        <v>1443.245483398438</v>
       </c>
       <c r="C237" t="n">
-        <v>719.8695068359375</v>
+        <v>719.8695678710938</v>
       </c>
       <c r="D237" t="n">
         <v>1340.6611328125</v>
@@ -3765,7 +3765,7 @@
         <v>45435</v>
       </c>
       <c r="B238" t="n">
-        <v>1468.342895507812</v>
+        <v>1468.343017578125</v>
       </c>
       <c r="C238" t="n">
         <v>736.3468017578125</v>
@@ -3782,7 +3782,7 @@
         <v>1462.611938476562</v>
       </c>
       <c r="C239" t="n">
-        <v>748.4827880859375</v>
+        <v>748.4827270507812</v>
       </c>
       <c r="D239" t="n">
         <v>1350.15283203125</v>
@@ -3799,7 +3799,7 @@
         <v>753.6627807617188</v>
       </c>
       <c r="D240" t="n">
-        <v>1355.912719726562</v>
+        <v>1355.91259765625</v>
       </c>
     </row>
     <row r="241">
@@ -3807,13 +3807,13 @@
         <v>45440</v>
       </c>
       <c r="B241" t="n">
-        <v>1438.848510742188</v>
+        <v>1438.8486328125</v>
       </c>
       <c r="C241" t="n">
-        <v>755.0440673828125</v>
+        <v>755.0441284179688</v>
       </c>
       <c r="D241" t="n">
-        <v>1351.950073242188</v>
+        <v>1351.949951171875</v>
       </c>
     </row>
     <row r="242">
@@ -3821,13 +3821,13 @@
         <v>45441</v>
       </c>
       <c r="B242" t="n">
-        <v>1423.607299804688</v>
+        <v>1423.607421875</v>
       </c>
       <c r="C242" t="n">
         <v>744.0921630859375</v>
       </c>
       <c r="D242" t="n">
-        <v>1337.113037109375</v>
+        <v>1337.113159179688</v>
       </c>
     </row>
     <row r="243">
@@ -3855,7 +3855,7 @@
         <v>755.5620727539062</v>
       </c>
       <c r="D244" t="n">
-        <v>1322.459838867188</v>
+        <v>1322.459716796875</v>
       </c>
     </row>
     <row r="245">
@@ -3866,10 +3866,10 @@
         <v>1492.32861328125</v>
       </c>
       <c r="C245" t="n">
-        <v>775.615966796875</v>
+        <v>775.6160278320312</v>
       </c>
       <c r="D245" t="n">
-        <v>1321.519897460938</v>
+        <v>1321.519775390625</v>
       </c>
     </row>
     <row r="246">
@@ -3880,10 +3880,10 @@
         <v>1380.625732421875</v>
       </c>
       <c r="C246" t="n">
-        <v>731.6848754882812</v>
+        <v>731.684814453125</v>
       </c>
       <c r="D246" t="n">
-        <v>1310.005126953125</v>
+        <v>1310.0048828125</v>
       </c>
     </row>
     <row r="247">
@@ -3897,7 +3897,7 @@
         <v>765.5520629882812</v>
       </c>
       <c r="D247" t="n">
-        <v>1344.267333984375</v>
+        <v>1344.267211914062</v>
       </c>
     </row>
     <row r="248">
@@ -3911,7 +3911,7 @@
         <v>769.4493408203125</v>
       </c>
       <c r="D248" t="n">
-        <v>1383.887451171875</v>
+        <v>1383.8876953125</v>
       </c>
     </row>
     <row r="249">
@@ -3922,10 +3922,10 @@
         <v>1452.4345703125</v>
       </c>
       <c r="C249" t="n">
-        <v>776.1832885742188</v>
+        <v>776.183349609375</v>
       </c>
       <c r="D249" t="n">
-        <v>1441.555419921875</v>
+        <v>1441.555297851562</v>
       </c>
     </row>
     <row r="250">
@@ -3936,10 +3936,10 @@
         <v>1453.867431640625</v>
       </c>
       <c r="C250" t="n">
-        <v>770.23876953125</v>
+        <v>770.2387084960938</v>
       </c>
       <c r="D250" t="n">
-        <v>1409.736938476562</v>
+        <v>1409.737060546875</v>
       </c>
     </row>
     <row r="251">
@@ -3947,13 +3947,13 @@
         <v>45454</v>
       </c>
       <c r="B251" t="n">
-        <v>1439.31787109375</v>
+        <v>1439.317993164062</v>
       </c>
       <c r="C251" t="n">
         <v>771.9653930664062</v>
       </c>
       <c r="D251" t="n">
-        <v>1405.977172851562</v>
+        <v>1405.97705078125</v>
       </c>
     </row>
     <row r="252">
@@ -3967,7 +3967,7 @@
         <v>776.5780029296875</v>
       </c>
       <c r="D252" t="n">
-        <v>1396.060180664062</v>
+        <v>1396.060302734375</v>
       </c>
     </row>
     <row r="253">
@@ -3981,7 +3981,7 @@
         <v>779.8340454101562</v>
       </c>
       <c r="D253" t="n">
-        <v>1404.285034179688</v>
+        <v>1404.28515625</v>
       </c>
     </row>
     <row r="254">
@@ -3992,7 +3992,7 @@
         <v>1459.944213867188</v>
       </c>
       <c r="C254" t="n">
-        <v>787.8013305664062</v>
+        <v>787.80126953125</v>
       </c>
       <c r="D254" t="n">
         <v>1399.538208007812</v>
@@ -4006,10 +4006,10 @@
         <v>1463.377807617188</v>
       </c>
       <c r="C255" t="n">
-        <v>793.1785888671875</v>
+        <v>793.1786499023438</v>
       </c>
       <c r="D255" t="n">
-        <v>1408.279907226562</v>
+        <v>1408.280029296875</v>
       </c>
     </row>
     <row r="256">
@@ -4017,13 +4017,13 @@
         <v>45462</v>
       </c>
       <c r="B256" t="n">
-        <v>1441.269409179688</v>
+        <v>1441.26953125</v>
       </c>
       <c r="C256" t="n">
         <v>817.869873046875</v>
       </c>
       <c r="D256" t="n">
-        <v>1420.640869140625</v>
+        <v>1420.640625</v>
       </c>
     </row>
     <row r="257">
@@ -4031,13 +4031,13 @@
         <v>45463</v>
       </c>
       <c r="B257" t="n">
-        <v>1456.140014648438</v>
+        <v>1456.139892578125</v>
       </c>
       <c r="C257" t="n">
         <v>823.5431518554688</v>
       </c>
       <c r="D257" t="n">
-        <v>1424.44775390625</v>
+        <v>1424.447631835938</v>
       </c>
     </row>
     <row r="258">
@@ -4045,13 +4045,13 @@
         <v>45464</v>
       </c>
       <c r="B258" t="n">
-        <v>1436.872314453125</v>
+        <v>1436.872436523438</v>
       </c>
       <c r="C258" t="n">
-        <v>821.7672119140625</v>
+        <v>821.7671508789062</v>
       </c>
       <c r="D258" t="n">
-        <v>1440.709228515625</v>
+        <v>1440.709350585938</v>
       </c>
     </row>
     <row r="259">
@@ -4059,7 +4059,7 @@
         <v>45467</v>
       </c>
       <c r="B259" t="n">
-        <v>1424.298950195312</v>
+        <v>1424.298828125</v>
       </c>
       <c r="C259" t="n">
         <v>825.0478515625</v>
@@ -4079,7 +4079,7 @@
         <v>844.2631225585938</v>
       </c>
       <c r="D260" t="n">
-        <v>1449.404052734375</v>
+        <v>1449.404174804688</v>
       </c>
     </row>
     <row r="261">
@@ -4093,7 +4093,7 @@
         <v>839.40380859375</v>
       </c>
       <c r="D261" t="n">
-        <v>1448.229248046875</v>
+        <v>1448.229125976562</v>
       </c>
     </row>
     <row r="262">
@@ -4101,7 +4101,7 @@
         <v>45470</v>
       </c>
       <c r="B262" t="n">
-        <v>1512.312622070312</v>
+        <v>1512.312744140625</v>
       </c>
       <c r="C262" t="n">
         <v>836.7644653320312</v>
@@ -4118,7 +4118,7 @@
         <v>1546.747436523438</v>
       </c>
       <c r="C263" t="n">
-        <v>830.671875</v>
+        <v>830.6718139648438</v>
       </c>
       <c r="D263" t="n">
         <v>1472.715698242188</v>
@@ -4132,7 +4132,7 @@
         <v>1541.559936523438</v>
       </c>
       <c r="C264" t="n">
-        <v>841.2290649414062</v>
+        <v>841.2291259765625</v>
       </c>
       <c r="D264" t="n">
         <v>1495.322387695312</v>
@@ -4143,13 +4143,13 @@
         <v>45475</v>
       </c>
       <c r="B265" t="n">
-        <v>1546.525146484375</v>
+        <v>1546.525024414062</v>
       </c>
       <c r="C265" t="n">
         <v>853.7597045898438</v>
       </c>
       <c r="D265" t="n">
-        <v>1523.7568359375</v>
+        <v>1523.756713867188</v>
       </c>
     </row>
     <row r="266">
@@ -4160,7 +4160,7 @@
         <v>1533.927001953125</v>
       </c>
       <c r="C266" t="n">
-        <v>872.531005859375</v>
+        <v>872.5310668945312</v>
       </c>
       <c r="D266" t="n">
         <v>1529.7255859375</v>
@@ -4191,7 +4191,7 @@
         <v>813.0598754882812</v>
       </c>
       <c r="D268" t="n">
-        <v>1548.572143554688</v>
+        <v>1548.572265625</v>
       </c>
     </row>
     <row r="269">
@@ -4213,7 +4213,7 @@
         <v>45482</v>
       </c>
       <c r="B270" t="n">
-        <v>1571.325927734375</v>
+        <v>1571.326049804688</v>
       </c>
       <c r="C270" t="n">
         <v>807.3372192382812</v>
@@ -4230,7 +4230,7 @@
         <v>1565.348022460938</v>
       </c>
       <c r="C271" t="n">
-        <v>802.20654296875</v>
+        <v>802.2066040039062</v>
       </c>
       <c r="D271" t="n">
         <v>1549.32421875</v>
@@ -4244,10 +4244,10 @@
         <v>1561.815673828125</v>
       </c>
       <c r="C272" t="n">
-        <v>800.1346435546875</v>
+        <v>800.1345825195312</v>
       </c>
       <c r="D272" t="n">
-        <v>1553.507202148438</v>
+        <v>1553.507080078125</v>
       </c>
     </row>
     <row r="273">
@@ -4255,13 +4255,13 @@
         <v>45485</v>
       </c>
       <c r="B273" t="n">
-        <v>1577.69921875</v>
+        <v>1577.699096679688</v>
       </c>
       <c r="C273" t="n">
         <v>800.5292358398438</v>
       </c>
       <c r="D273" t="n">
-        <v>1609.012939453125</v>
+        <v>1609.013061523438</v>
       </c>
     </row>
     <row r="274">
@@ -4283,10 +4283,10 @@
         <v>45489</v>
       </c>
       <c r="B275" t="n">
-        <v>1557.468139648438</v>
+        <v>1557.468017578125</v>
       </c>
       <c r="C275" t="n">
-        <v>799.0739135742188</v>
+        <v>799.073974609375</v>
       </c>
       <c r="D275" t="n">
         <v>1622.454833984375</v>
@@ -4297,10 +4297,10 @@
         <v>45491</v>
       </c>
       <c r="B276" t="n">
-        <v>1567.768920898438</v>
+        <v>1567.76904296875</v>
       </c>
       <c r="C276" t="n">
-        <v>796.6320190429688</v>
+        <v>796.6319580078125</v>
       </c>
       <c r="D276" t="n">
         <v>1652.534301757812</v>
@@ -4314,10 +4314,10 @@
         <v>1536.61962890625</v>
       </c>
       <c r="C277" t="n">
-        <v>792.9319458007812</v>
+        <v>792.9320068359375</v>
       </c>
       <c r="D277" t="n">
-        <v>1685.339477539062</v>
+        <v>1685.339599609375</v>
       </c>
     </row>
     <row r="278">
@@ -4325,13 +4325,13 @@
         <v>45495</v>
       </c>
       <c r="B278" t="n">
-        <v>1482.793701171875</v>
+        <v>1482.793579101562</v>
       </c>
       <c r="C278" t="n">
         <v>810.3218994140625</v>
       </c>
       <c r="D278" t="n">
-        <v>1702.1650390625</v>
+        <v>1702.165283203125</v>
       </c>
     </row>
     <row r="279">
@@ -4339,7 +4339,7 @@
         <v>45496</v>
       </c>
       <c r="B279" t="n">
-        <v>1470.1708984375</v>
+        <v>1470.170776367188</v>
       </c>
       <c r="C279" t="n">
         <v>798.407958984375</v>
@@ -4353,7 +4353,7 @@
         <v>45497</v>
       </c>
       <c r="B280" t="n">
-        <v>1477.8779296875</v>
+        <v>1477.877807617188</v>
       </c>
       <c r="C280" t="n">
         <v>791.3286743164062</v>
@@ -4370,10 +4370,10 @@
         <v>1474.6171875</v>
       </c>
       <c r="C281" t="n">
-        <v>797.5198974609375</v>
+        <v>797.5199584960938</v>
       </c>
       <c r="D281" t="n">
-        <v>1715.325073242188</v>
+        <v>1715.324829101562</v>
       </c>
     </row>
     <row r="282">
@@ -4395,7 +4395,7 @@
         <v>45502</v>
       </c>
       <c r="B283" t="n">
-        <v>1501.987182617188</v>
+        <v>1501.987060546875</v>
       </c>
       <c r="C283" t="n">
         <v>791.822021484375</v>
@@ -4412,7 +4412,7 @@
         <v>1495.119995117188</v>
       </c>
       <c r="C284" t="n">
-        <v>797.0020141601562</v>
+        <v>797.001953125</v>
       </c>
       <c r="D284" t="n">
         <v>1764.485961914062</v>
@@ -4423,13 +4423,13 @@
         <v>45504</v>
       </c>
       <c r="B285" t="n">
-        <v>1487.486938476562</v>
+        <v>1487.487060546875</v>
       </c>
       <c r="C285" t="n">
-        <v>797.1006469726562</v>
+        <v>797.1005859375</v>
       </c>
       <c r="D285" t="n">
-        <v>1756.119995117188</v>
+        <v>1756.1201171875</v>
       </c>
     </row>
     <row r="286">
@@ -4454,7 +4454,7 @@
         <v>1481.459594726562</v>
       </c>
       <c r="C287" t="n">
-        <v>818.51123046875</v>
+        <v>818.5111694335938</v>
       </c>
       <c r="D287" t="n">
         <v>1711.893920898438</v>
@@ -4465,13 +4465,13 @@
         <v>45509</v>
       </c>
       <c r="B288" t="n">
-        <v>1430.079223632812</v>
+        <v>1430.079345703125</v>
       </c>
       <c r="C288" t="n">
-        <v>797.1006469726562</v>
+        <v>797.1005859375</v>
       </c>
       <c r="D288" t="n">
-        <v>1646.753295898438</v>
+        <v>1646.75341796875</v>
       </c>
     </row>
     <row r="289">
@@ -4479,7 +4479,7 @@
         <v>45510</v>
       </c>
       <c r="B289" t="n">
-        <v>1438.700439453125</v>
+        <v>1438.700317382812</v>
       </c>
       <c r="C289" t="n">
         <v>789.922607421875</v>
@@ -4496,7 +4496,7 @@
         <v>1447.370727539062</v>
       </c>
       <c r="C290" t="n">
-        <v>800.9239501953125</v>
+        <v>800.9238891601562</v>
       </c>
       <c r="D290" t="n">
         <v>1684.11767578125</v>
@@ -4507,7 +4507,7 @@
         <v>45512</v>
       </c>
       <c r="B291" t="n">
-        <v>1431.85791015625</v>
+        <v>1431.857788085938</v>
       </c>
       <c r="C291" t="n">
         <v>810.3958740234375</v>
@@ -4524,7 +4524,7 @@
         <v>1456.733032226562</v>
       </c>
       <c r="C292" t="n">
-        <v>814.0958862304688</v>
+        <v>814.0958251953125</v>
       </c>
       <c r="D292" t="n">
         <v>1664.471923828125</v>
@@ -4535,10 +4535,10 @@
         <v>45516</v>
       </c>
       <c r="B293" t="n">
-        <v>1443.220947265625</v>
+        <v>1443.220703125</v>
       </c>
       <c r="C293" t="n">
-        <v>818.9797973632812</v>
+        <v>818.9798583984375</v>
       </c>
       <c r="D293" t="n">
         <v>1689.5224609375</v>
@@ -4552,10 +4552,10 @@
         <v>1446.185180664062</v>
       </c>
       <c r="C294" t="n">
-        <v>790.9093017578125</v>
+        <v>790.9092407226562</v>
       </c>
       <c r="D294" t="n">
-        <v>1689.5693359375</v>
+        <v>1689.569458007812</v>
       </c>
     </row>
     <row r="295">
@@ -4563,10 +4563,10 @@
         <v>45518</v>
       </c>
       <c r="B295" t="n">
-        <v>1444.431274414062</v>
+        <v>1444.43115234375</v>
       </c>
       <c r="C295" t="n">
-        <v>793.1785888671875</v>
+        <v>793.1786499023438</v>
       </c>
       <c r="D295" t="n">
         <v>1713.821044921875</v>
@@ -4577,13 +4577,13 @@
         <v>45520</v>
       </c>
       <c r="B296" t="n">
-        <v>1460.586303710938</v>
+        <v>1460.58642578125</v>
       </c>
       <c r="C296" t="n">
-        <v>805.1665649414062</v>
+        <v>805.1666259765625</v>
       </c>
       <c r="D296" t="n">
-        <v>1747.378295898438</v>
+        <v>1747.378173828125</v>
       </c>
     </row>
     <row r="297">
@@ -4608,10 +4608,10 @@
         <v>1483.1416015625</v>
       </c>
       <c r="C298" t="n">
-        <v>807.92919921875</v>
+        <v>807.9292602539062</v>
       </c>
       <c r="D298" t="n">
-        <v>1759.833129882812</v>
+        <v>1759.832885742188</v>
       </c>
     </row>
     <row r="299">
@@ -4622,10 +4622,10 @@
         <v>1485.843383789062</v>
       </c>
       <c r="C299" t="n">
-        <v>802.05859375</v>
+        <v>802.0586547851562</v>
       </c>
       <c r="D299" t="n">
-        <v>1760.302856445312</v>
+        <v>1760.302978515625</v>
       </c>
     </row>
     <row r="300">
@@ -4653,7 +4653,7 @@
         <v>801.6885986328125</v>
       </c>
       <c r="D301" t="n">
-        <v>1750.339233398438</v>
+        <v>1750.339111328125</v>
       </c>
     </row>
     <row r="302">
@@ -4661,7 +4661,7 @@
         <v>45530</v>
       </c>
       <c r="B302" t="n">
-        <v>1499.649047851562</v>
+        <v>1499.649169921875</v>
       </c>
       <c r="C302" t="n">
         <v>809.0392456054688</v>
@@ -4681,7 +4681,7 @@
         <v>807.9539184570312</v>
       </c>
       <c r="D303" t="n">
-        <v>1786.05859375</v>
+        <v>1786.058471679688</v>
       </c>
     </row>
     <row r="304">
@@ -4689,7 +4689,7 @@
         <v>45532</v>
       </c>
       <c r="B304" t="n">
-        <v>1485.471557617188</v>
+        <v>1485.4716796875</v>
       </c>
       <c r="C304" t="n">
         <v>807.6332397460938</v>
@@ -4709,7 +4709,7 @@
         <v>808.3485717773438</v>
       </c>
       <c r="D305" t="n">
-        <v>1817.31298828125</v>
+        <v>1817.312866210938</v>
       </c>
     </row>
     <row r="306">
@@ -4723,7 +4723,7 @@
         <v>807.5346069335938</v>
       </c>
       <c r="D306" t="n">
-        <v>1827.041748046875</v>
+        <v>1827.041625976562</v>
       </c>
     </row>
     <row r="307">
@@ -4731,13 +4731,13 @@
         <v>45537</v>
       </c>
       <c r="B307" t="n">
-        <v>1503.267822265625</v>
+        <v>1503.267944335938</v>
       </c>
       <c r="C307" t="n">
         <v>802.6258544921875</v>
       </c>
       <c r="D307" t="n">
-        <v>1846.59326171875</v>
+        <v>1846.593383789062</v>
       </c>
     </row>
     <row r="308">
@@ -4748,10 +4748,10 @@
         <v>1496.203857421875</v>
       </c>
       <c r="C308" t="n">
-        <v>807.7565307617188</v>
+        <v>807.756591796875</v>
       </c>
       <c r="D308" t="n">
-        <v>1824.738647460938</v>
+        <v>1824.738891601562</v>
       </c>
     </row>
     <row r="309">
@@ -4762,7 +4762,7 @@
         <v>1501.582397460938</v>
       </c>
       <c r="C309" t="n">
-        <v>809.9519653320312</v>
+        <v>809.951904296875</v>
       </c>
       <c r="D309" t="n">
         <v>1807.067016601562</v>
@@ -4779,7 +4779,7 @@
         <v>811.7525024414062</v>
       </c>
       <c r="D310" t="n">
-        <v>1817.125</v>
+        <v>1817.124877929688</v>
       </c>
     </row>
     <row r="311">
@@ -4793,7 +4793,7 @@
         <v>807.5592041015625</v>
       </c>
       <c r="D311" t="n">
-        <v>1787.703369140625</v>
+        <v>1787.703491210938</v>
       </c>
     </row>
     <row r="312">
@@ -4801,13 +4801,13 @@
         <v>45544</v>
       </c>
       <c r="B312" t="n">
-        <v>1449.928344726562</v>
+        <v>1449.928466796875</v>
       </c>
       <c r="C312" t="n">
         <v>812.2705688476562</v>
       </c>
       <c r="D312" t="n">
-        <v>1780.935791015625</v>
+        <v>1780.935668945312</v>
       </c>
     </row>
     <row r="313">
@@ -4815,10 +4815,10 @@
         <v>45545</v>
       </c>
       <c r="B313" t="n">
-        <v>1449.011352539062</v>
+        <v>1449.011474609375</v>
       </c>
       <c r="C313" t="n">
-        <v>814.169921875</v>
+        <v>814.1698608398438</v>
       </c>
       <c r="D313" t="n">
         <v>1797.5263671875</v>
@@ -4829,7 +4829,7 @@
         <v>45546</v>
       </c>
       <c r="B314" t="n">
-        <v>1439.072143554688</v>
+        <v>1439.072265625</v>
       </c>
       <c r="C314" t="n">
         <v>810.9879150390625</v>
@@ -4849,7 +4849,7 @@
         <v>822.1865234375</v>
       </c>
       <c r="D315" t="n">
-        <v>1833.386474609375</v>
+        <v>1833.386596679688</v>
       </c>
     </row>
     <row r="316">
@@ -4863,7 +4863,7 @@
         <v>821.8658447265625</v>
       </c>
       <c r="D316" t="n">
-        <v>1827.417724609375</v>
+        <v>1827.417846679688</v>
       </c>
     </row>
     <row r="317">
@@ -4871,13 +4871,13 @@
         <v>45551</v>
       </c>
       <c r="B317" t="n">
-        <v>1458.752197265625</v>
+        <v>1458.752319335938</v>
       </c>
       <c r="C317" t="n">
         <v>824.3324584960938</v>
       </c>
       <c r="D317" t="n">
-        <v>1833.198486328125</v>
+        <v>1833.198608398438</v>
       </c>
     </row>
     <row r="318">
@@ -4899,10 +4899,10 @@
         <v>45553</v>
       </c>
       <c r="B319" t="n">
-        <v>1450.919921875</v>
+        <v>1450.919799804688</v>
       </c>
       <c r="C319" t="n">
-        <v>836.0985107421875</v>
+        <v>836.0984497070312</v>
       </c>
       <c r="D319" t="n">
         <v>1778.585693359375</v>
@@ -4919,7 +4919,7 @@
         <v>842.8571166992188</v>
       </c>
       <c r="D320" t="n">
-        <v>1780.5126953125</v>
+        <v>1780.512573242188</v>
       </c>
     </row>
     <row r="321">
@@ -4933,7 +4933,7 @@
         <v>858.989013671875</v>
       </c>
       <c r="D321" t="n">
-        <v>1791.36962890625</v>
+        <v>1791.369506835938</v>
       </c>
     </row>
     <row r="322">
@@ -4944,10 +4944,10 @@
         <v>1480.588745117188</v>
       </c>
       <c r="C322" t="n">
-        <v>868.1650390625</v>
+        <v>868.1651000976562</v>
       </c>
       <c r="D322" t="n">
-        <v>1782.627563476562</v>
+        <v>1782.627685546875</v>
       </c>
     </row>
     <row r="323">
@@ -4972,10 +4972,10 @@
         <v>1481.15869140625</v>
       </c>
       <c r="C324" t="n">
-        <v>877.6863403320312</v>
+        <v>877.686279296875</v>
       </c>
       <c r="D324" t="n">
-        <v>1781.546752929688</v>
+        <v>1781.546630859375</v>
       </c>
     </row>
     <row r="325">
@@ -4986,10 +4986,10 @@
         <v>1485.12451171875</v>
       </c>
       <c r="C325" t="n">
-        <v>879.832275390625</v>
+        <v>879.8323364257812</v>
       </c>
       <c r="D325" t="n">
-        <v>1786.199462890625</v>
+        <v>1786.199584960938</v>
       </c>
     </row>
     <row r="326">
@@ -5000,10 +5000,10 @@
         <v>1513.10791015625</v>
       </c>
       <c r="C326" t="n">
-        <v>864.6377563476562</v>
+        <v>864.6376953125</v>
       </c>
       <c r="D326" t="n">
-        <v>1792.309448242188</v>
+        <v>1792.3095703125</v>
       </c>
     </row>
     <row r="327">
@@ -5017,7 +5017,7 @@
         <v>854.47509765625</v>
       </c>
       <c r="D327" t="n">
-        <v>1763.028930664062</v>
+        <v>1763.029174804688</v>
       </c>
     </row>
     <row r="328">
@@ -5045,7 +5045,7 @@
         <v>829.7838134765625</v>
       </c>
       <c r="D329" t="n">
-        <v>1779.7607421875</v>
+        <v>1779.760620117188</v>
       </c>
     </row>
     <row r="330">
@@ -5059,7 +5059,7 @@
         <v>817.771240234375</v>
       </c>
       <c r="D330" t="n">
-        <v>1803.025146484375</v>
+        <v>1803.025268554688</v>
       </c>
     </row>
     <row r="331">
@@ -5067,7 +5067,7 @@
         <v>45572</v>
       </c>
       <c r="B331" t="n">
-        <v>1358.988891601562</v>
+        <v>1358.98876953125</v>
       </c>
       <c r="C331" t="n">
         <v>798.1119384765625</v>
@@ -5081,13 +5081,13 @@
         <v>45573</v>
       </c>
       <c r="B332" t="n">
-        <v>1385.385864257812</v>
+        <v>1385.3857421875</v>
       </c>
       <c r="C332" t="n">
-        <v>814.5151977539062</v>
+        <v>814.5152587890625</v>
       </c>
       <c r="D332" t="n">
-        <v>1831.6005859375</v>
+        <v>1831.600708007812</v>
       </c>
     </row>
     <row r="333">
@@ -5098,10 +5098,10 @@
         <v>1362.830688476562</v>
       </c>
       <c r="C333" t="n">
-        <v>805.6846313476562</v>
+        <v>805.6845703125</v>
       </c>
       <c r="D333" t="n">
-        <v>1835.548461914062</v>
+        <v>1835.548583984375</v>
       </c>
     </row>
     <row r="334">
@@ -5115,7 +5115,7 @@
         <v>820.114501953125</v>
       </c>
       <c r="D334" t="n">
-        <v>1803.82421875</v>
+        <v>1803.824096679688</v>
       </c>
     </row>
     <row r="335">
@@ -5126,10 +5126,10 @@
         <v>1360.35205078125</v>
       </c>
       <c r="C335" t="n">
-        <v>814.4906005859375</v>
+        <v>814.4905395507812</v>
       </c>
       <c r="D335" t="n">
-        <v>1818.957885742188</v>
+        <v>1818.9580078125</v>
       </c>
     </row>
     <row r="336">
@@ -5143,7 +5143,7 @@
         <v>832.7931518554688</v>
       </c>
       <c r="D336" t="n">
-        <v>1841.329467773438</v>
+        <v>1841.329345703125</v>
       </c>
     </row>
     <row r="337">
@@ -5165,13 +5165,13 @@
         <v>45581</v>
       </c>
       <c r="B338" t="n">
-        <v>1342.481323242188</v>
+        <v>1342.4814453125</v>
       </c>
       <c r="C338" t="n">
         <v>838.565185546875</v>
       </c>
       <c r="D338" t="n">
-        <v>1804.858276367188</v>
+        <v>1804.858154296875</v>
       </c>
     </row>
     <row r="339">
@@ -5207,7 +5207,7 @@
         <v>45586</v>
       </c>
       <c r="B341" t="n">
-        <v>1357.476806640625</v>
+        <v>1357.476928710938</v>
       </c>
       <c r="C341" t="n">
         <v>852.8223876953125</v>
@@ -5221,13 +5221,13 @@
         <v>45587</v>
       </c>
       <c r="B342" t="n">
-        <v>1331.848266601562</v>
+        <v>1331.84814453125</v>
       </c>
       <c r="C342" t="n">
         <v>845.841796875</v>
       </c>
       <c r="D342" t="n">
-        <v>1740.46923828125</v>
+        <v>1740.469360351562</v>
       </c>
     </row>
     <row r="343">
@@ -5235,13 +5235,13 @@
         <v>45588</v>
       </c>
       <c r="B343" t="n">
-        <v>1327.064575195312</v>
+        <v>1327.064453125</v>
       </c>
       <c r="C343" t="n">
         <v>856.3251342773438</v>
       </c>
       <c r="D343" t="n">
-        <v>1760.961181640625</v>
+        <v>1760.961059570312</v>
       </c>
     </row>
     <row r="344">
@@ -5269,7 +5269,7 @@
         <v>860.0744018554688</v>
       </c>
       <c r="D345" t="n">
-        <v>1750.292236328125</v>
+        <v>1750.292358398438</v>
       </c>
     </row>
     <row r="346">
@@ -5283,7 +5283,7 @@
         <v>855.5357055664062</v>
       </c>
       <c r="D346" t="n">
-        <v>1753.394287109375</v>
+        <v>1753.394165039062</v>
       </c>
     </row>
     <row r="347">
@@ -5297,7 +5297,7 @@
         <v>864.2430419921875</v>
       </c>
       <c r="D347" t="n">
-        <v>1748.593383789062</v>
+        <v>1748.59326171875</v>
       </c>
     </row>
     <row r="348">
@@ -5308,10 +5308,10 @@
         <v>1332.3935546875</v>
       </c>
       <c r="C348" t="n">
-        <v>855.7330932617188</v>
+        <v>855.7330322265625</v>
       </c>
       <c r="D348" t="n">
-        <v>1713.227661132812</v>
+        <v>1713.227783203125</v>
       </c>
     </row>
     <row r="349">
@@ -5322,10 +5322,10 @@
         <v>1320.64501953125</v>
       </c>
       <c r="C349" t="n">
-        <v>856.2756958007812</v>
+        <v>856.2757568359375</v>
       </c>
       <c r="D349" t="n">
-        <v>1670.589721679688</v>
+        <v>1670.589599609375</v>
       </c>
     </row>
     <row r="350">
@@ -5336,7 +5336,7 @@
         <v>1327.1884765625</v>
       </c>
       <c r="C350" t="n">
-        <v>857.0651245117188</v>
+        <v>857.0650634765625</v>
       </c>
       <c r="D350" t="n">
         <v>1674.011962890625</v>
@@ -5353,7 +5353,7 @@
         <v>845.6197509765625</v>
       </c>
       <c r="D351" t="n">
-        <v>1676.674072265625</v>
+        <v>1676.673950195312</v>
       </c>
     </row>
     <row r="352">
@@ -5375,13 +5375,13 @@
         <v>45602</v>
       </c>
       <c r="B353" t="n">
-        <v>1314.002197265625</v>
+        <v>1314.002319335938</v>
       </c>
       <c r="C353" t="n">
-        <v>865.92041015625</v>
+        <v>865.9203491210938</v>
       </c>
       <c r="D353" t="n">
-        <v>1733.762451171875</v>
+        <v>1733.762573242188</v>
       </c>
     </row>
     <row r="354">
@@ -5389,7 +5389,7 @@
         <v>45603</v>
       </c>
       <c r="B354" t="n">
-        <v>1294.470947265625</v>
+        <v>1294.471069335938</v>
       </c>
       <c r="C354" t="n">
         <v>861.62841796875</v>
@@ -5403,10 +5403,10 @@
         <v>45604</v>
       </c>
       <c r="B355" t="n">
-        <v>1272.758544921875</v>
+        <v>1272.758422851562</v>
       </c>
       <c r="C355" t="n">
-        <v>865.5256958007812</v>
+        <v>865.525634765625</v>
       </c>
       <c r="D355" t="n">
         <v>1739.704345703125</v>
@@ -5434,7 +5434,7 @@
         <v>1263.33984375</v>
       </c>
       <c r="C357" t="n">
-        <v>847.6423950195312</v>
+        <v>847.6424560546875</v>
       </c>
       <c r="D357" t="n">
         <v>1776.638427734375</v>
@@ -5451,7 +5451,7 @@
         <v>829.463134765625</v>
       </c>
       <c r="D358" t="n">
-        <v>1776.258056640625</v>
+        <v>1776.258178710938</v>
       </c>
     </row>
     <row r="359">
@@ -5479,7 +5479,7 @@
         <v>841.1797485351562</v>
       </c>
       <c r="D360" t="n">
-        <v>1722.11669921875</v>
+        <v>1722.116577148438</v>
       </c>
     </row>
     <row r="361">
@@ -5501,7 +5501,7 @@
         <v>45617</v>
       </c>
       <c r="B362" t="n">
-        <v>1212.528564453125</v>
+        <v>1212.528686523438</v>
       </c>
       <c r="C362" t="n">
         <v>858.989013671875</v>
@@ -5515,10 +5515,10 @@
         <v>45618</v>
       </c>
       <c r="B363" t="n">
-        <v>1254.565673828125</v>
+        <v>1254.565551757812</v>
       </c>
       <c r="C363" t="n">
-        <v>861.1597290039062</v>
+        <v>861.15966796875</v>
       </c>
       <c r="D363" t="n">
         <v>1808.438842773438</v>
@@ -5535,7 +5535,7 @@
         <v>880.8929443359375</v>
       </c>
       <c r="D364" t="n">
-        <v>1796.507568359375</v>
+        <v>1796.507690429688</v>
       </c>
     </row>
     <row r="365">
@@ -5543,7 +5543,7 @@
         <v>45622</v>
       </c>
       <c r="B365" t="n">
-        <v>1284.606079101562</v>
+        <v>1284.606201171875</v>
       </c>
       <c r="C365" t="n">
         <v>880.8683471679688</v>
@@ -5563,7 +5563,7 @@
         <v>894.06494140625</v>
       </c>
       <c r="D366" t="n">
-        <v>1829.591552734375</v>
+        <v>1829.591430664062</v>
       </c>
     </row>
     <row r="367">
@@ -5577,7 +5577,7 @@
         <v>884.6176147460938</v>
       </c>
       <c r="D367" t="n">
-        <v>1765.087646484375</v>
+        <v>1765.087524414062</v>
       </c>
     </row>
     <row r="368">
@@ -5599,7 +5599,7 @@
         <v>45628</v>
       </c>
       <c r="B369" t="n">
-        <v>1297.941040039062</v>
+        <v>1297.941162109375</v>
       </c>
       <c r="C369" t="n">
         <v>890.3156127929688</v>
@@ -5613,7 +5613,7 @@
         <v>45629</v>
       </c>
       <c r="B370" t="n">
-        <v>1311.969970703125</v>
+        <v>1311.969848632812</v>
       </c>
       <c r="C370" t="n">
         <v>900.9715576171875</v>
@@ -5655,13 +5655,13 @@
         <v>45632</v>
       </c>
       <c r="B373" t="n">
-        <v>1300.320556640625</v>
+        <v>1300.320434570312</v>
       </c>
       <c r="C373" t="n">
         <v>915.5494995117188</v>
       </c>
       <c r="D373" t="n">
-        <v>1827.594970703125</v>
+        <v>1827.595092773438</v>
       </c>
     </row>
     <row r="374">
@@ -5672,7 +5672,7 @@
         <v>1284.060913085938</v>
       </c>
       <c r="C374" t="n">
-        <v>922.5301513671875</v>
+        <v>922.5302124023438</v>
       </c>
       <c r="D374" t="n">
         <v>1828.783447265625</v>
@@ -5725,13 +5725,13 @@
         <v>45639</v>
       </c>
       <c r="B378" t="n">
-        <v>1261.951782226562</v>
+        <v>1261.951904296875</v>
       </c>
       <c r="C378" t="n">
         <v>923.3934936523438</v>
       </c>
       <c r="D378" t="n">
-        <v>1901.0830078125</v>
+        <v>1901.082885742188</v>
       </c>
     </row>
     <row r="379">
@@ -5739,7 +5739,7 @@
         <v>45642</v>
       </c>
       <c r="B379" t="n">
-        <v>1257.440795898438</v>
+        <v>1257.44091796875</v>
       </c>
       <c r="C379" t="n">
         <v>920.1621704101562</v>
@@ -5753,7 +5753,7 @@
         <v>45643</v>
       </c>
       <c r="B380" t="n">
-        <v>1234.637817382812</v>
+        <v>1234.6376953125</v>
       </c>
       <c r="C380" t="n">
         <v>904.4002685546875</v>
@@ -5770,10 +5770,10 @@
         <v>1242.519653320312</v>
       </c>
       <c r="C381" t="n">
-        <v>893.2755737304688</v>
+        <v>893.275634765625</v>
       </c>
       <c r="D381" t="n">
-        <v>1881.546508789062</v>
+        <v>1881.54638671875</v>
       </c>
     </row>
     <row r="382">
@@ -5795,13 +5795,13 @@
         <v>45646</v>
       </c>
       <c r="B383" t="n">
-        <v>1194.980346679688</v>
+        <v>1194.980224609375</v>
       </c>
       <c r="C383" t="n">
         <v>873.93701171875</v>
       </c>
       <c r="D383" t="n">
-        <v>1827.357543945312</v>
+        <v>1827.357299804688</v>
       </c>
     </row>
     <row r="384">
@@ -5823,13 +5823,13 @@
         <v>45650</v>
       </c>
       <c r="B385" t="n">
-        <v>1212.280883789062</v>
+        <v>1212.28076171875</v>
       </c>
       <c r="C385" t="n">
         <v>887.0596313476562</v>
       </c>
       <c r="D385" t="n">
-        <v>1814.903564453125</v>
+        <v>1814.903442382812</v>
       </c>
     </row>
     <row r="386">
@@ -5857,7 +5857,7 @@
         <v>887.1336669921875</v>
       </c>
       <c r="D387" t="n">
-        <v>1822.223754882812</v>
+        <v>1822.2236328125</v>
       </c>
     </row>
     <row r="388">
@@ -5865,13 +5865,13 @@
         <v>45656</v>
       </c>
       <c r="B388" t="n">
-        <v>1200.333862304688</v>
+        <v>1200.333984375</v>
       </c>
       <c r="C388" t="n">
         <v>877.0943603515625</v>
       </c>
       <c r="D388" t="n">
-        <v>1812.003784179688</v>
+        <v>1812.00390625</v>
       </c>
     </row>
     <row r="389">
@@ -5882,10 +5882,10 @@
         <v>1205.043212890625</v>
       </c>
       <c r="C389" t="n">
-        <v>874.60302734375</v>
+        <v>874.6029663085938</v>
       </c>
       <c r="D389" t="n">
-        <v>1787.2861328125</v>
+        <v>1787.286010742188</v>
       </c>
     </row>
     <row r="390">
@@ -5896,10 +5896,10 @@
         <v>1210.793579101562</v>
       </c>
       <c r="C390" t="n">
-        <v>879.4869384765625</v>
+        <v>879.4869995117188</v>
       </c>
       <c r="D390" t="n">
-        <v>1789.662841796875</v>
+        <v>1789.662719726562</v>
       </c>
     </row>
     <row r="391">
@@ -5921,13 +5921,13 @@
         <v>45660</v>
       </c>
       <c r="B392" t="n">
-        <v>1240.437622070312</v>
+        <v>1240.437744140625</v>
       </c>
       <c r="C392" t="n">
         <v>862.9356689453125</v>
       </c>
       <c r="D392" t="n">
-        <v>1843.138916015625</v>
+        <v>1843.138793945312</v>
       </c>
     </row>
     <row r="393">
@@ -5935,13 +5935,13 @@
         <v>45663</v>
       </c>
       <c r="B393" t="n">
-        <v>1207.571533203125</v>
+        <v>1207.571411132812</v>
       </c>
       <c r="C393" t="n">
-        <v>843.8438110351562</v>
+        <v>843.84375</v>
       </c>
       <c r="D393" t="n">
-        <v>1842.283203125</v>
+        <v>1842.283081054688</v>
       </c>
     </row>
     <row r="394">
@@ -5955,7 +5955,7 @@
         <v>845.2744140625</v>
       </c>
       <c r="D394" t="n">
-        <v>1835.628295898438</v>
+        <v>1835.62841796875</v>
       </c>
     </row>
     <row r="395">
@@ -5977,7 +5977,7 @@
         <v>45666</v>
       </c>
       <c r="B396" t="n">
-        <v>1244.0068359375</v>
+        <v>1244.006713867188</v>
       </c>
       <c r="C396" t="n">
         <v>822.778564453125</v>
@@ -5997,7 +5997,7 @@
         <v>817.3272094726562</v>
       </c>
       <c r="D397" t="n">
-        <v>1869.947875976562</v>
+        <v>1869.947998046875</v>
       </c>
     </row>
     <row r="398">
@@ -6011,7 +6011,7 @@
         <v>804.5499267578125</v>
       </c>
       <c r="D398" t="n">
-        <v>1865.432373046875</v>
+        <v>1865.432250976562</v>
       </c>
     </row>
     <row r="399">
@@ -6036,7 +6036,7 @@
         <v>1241.478515625</v>
       </c>
       <c r="C400" t="n">
-        <v>810.5685424804688</v>
+        <v>810.568603515625</v>
       </c>
       <c r="D400" t="n">
         <v>1853.501220703125</v>
@@ -6050,7 +6050,7 @@
         <v>1255.606567382812</v>
       </c>
       <c r="C401" t="n">
-        <v>815.008544921875</v>
+        <v>815.0086059570312</v>
       </c>
       <c r="D401" t="n">
         <v>1833.3466796875</v>
@@ -6078,10 +6078,10 @@
         <v>1294.272705078125</v>
       </c>
       <c r="C403" t="n">
-        <v>814.6138305664062</v>
+        <v>814.6138916015625</v>
       </c>
       <c r="D403" t="n">
-        <v>1723.87548828125</v>
+        <v>1723.875610351562</v>
       </c>
     </row>
     <row r="404">
@@ -6092,7 +6092,7 @@
         <v>1262.794555664062</v>
       </c>
       <c r="C404" t="n">
-        <v>810.2478637695312</v>
+        <v>810.2479248046875</v>
       </c>
       <c r="D404" t="n">
         <v>1711.896728515625</v>
@@ -6103,13 +6103,13 @@
         <v>45679</v>
       </c>
       <c r="B405" t="n">
-        <v>1266.16552734375</v>
+        <v>1266.165405273438</v>
       </c>
       <c r="C405" t="n">
         <v>821.9152221679688</v>
       </c>
       <c r="D405" t="n">
-        <v>1764.8974609375</v>
+        <v>1764.897338867188</v>
       </c>
     </row>
     <row r="406">
@@ -6117,13 +6117,13 @@
         <v>45680</v>
       </c>
       <c r="B406" t="n">
-        <v>1252.830688476562</v>
+        <v>1252.83056640625</v>
       </c>
       <c r="C406" t="n">
         <v>821.347900390625</v>
       </c>
       <c r="D406" t="n">
-        <v>1773.45361328125</v>
+        <v>1773.453491210938</v>
       </c>
     </row>
     <row r="407">
@@ -6151,7 +6151,7 @@
         <v>804.0319213867188</v>
       </c>
       <c r="D408" t="n">
-        <v>1732.146362304688</v>
+        <v>1732.146484375</v>
       </c>
     </row>
     <row r="409">
@@ -6159,10 +6159,10 @@
         <v>45685</v>
       </c>
       <c r="B409" t="n">
-        <v>1223.8310546875</v>
+        <v>1223.831176757812</v>
       </c>
       <c r="C409" t="n">
-        <v>824.0611572265625</v>
+        <v>824.0612182617188</v>
       </c>
       <c r="D409" t="n">
         <v>1739.514282226562</v>
@@ -6179,7 +6179,7 @@
         <v>827.4651489257812</v>
       </c>
       <c r="D410" t="n">
-        <v>1788.474487304688</v>
+        <v>1788.474365234375</v>
       </c>
     </row>
     <row r="411">
@@ -6190,10 +6190,10 @@
         <v>1242.321411132812</v>
       </c>
       <c r="C411" t="n">
-        <v>834.470458984375</v>
+        <v>834.4705200195312</v>
       </c>
       <c r="D411" t="n">
-        <v>1768.224853515625</v>
+        <v>1768.224731445312</v>
       </c>
     </row>
     <row r="412">
@@ -6218,10 +6218,10 @@
         <v>1253.7724609375</v>
       </c>
       <c r="C413" t="n">
-        <v>834.1990966796875</v>
+        <v>834.1991577148438</v>
       </c>
       <c r="D413" t="n">
-        <v>1760.049072265625</v>
+        <v>1760.048950195312</v>
       </c>
     </row>
     <row r="414">
@@ -6235,7 +6235,7 @@
         <v>827.8104858398438</v>
       </c>
       <c r="D414" t="n">
-        <v>1771.40966796875</v>
+        <v>1771.409790039062</v>
       </c>
     </row>
     <row r="415">
@@ -6249,7 +6249,7 @@
         <v>848.9744873046875</v>
       </c>
       <c r="D415" t="n">
-        <v>1805.158935546875</v>
+        <v>1805.159057617188</v>
       </c>
     </row>
     <row r="416">
@@ -6277,7 +6277,7 @@
         <v>860.29638671875</v>
       </c>
       <c r="D417" t="n">
-        <v>1821.178100585938</v>
+        <v>1821.177978515625</v>
       </c>
     </row>
     <row r="418">
@@ -6288,7 +6288,7 @@
         <v>1255.8544921875</v>
       </c>
       <c r="C418" t="n">
-        <v>854.8203735351562</v>
+        <v>854.8204345703125</v>
       </c>
       <c r="D418" t="n">
         <v>1809.769775390625</v>
@@ -6302,7 +6302,7 @@
         <v>1242.916259765625</v>
       </c>
       <c r="C419" t="n">
-        <v>846.4337768554688</v>
+        <v>846.4337158203125</v>
       </c>
       <c r="D419" t="n">
         <v>1787.5712890625</v>
@@ -6316,7 +6316,7 @@
         <v>1224.277221679688</v>
       </c>
       <c r="C420" t="n">
-        <v>839.3544921875</v>
+        <v>839.3544311523438</v>
       </c>
       <c r="D420" t="n">
         <v>1783.150634765625</v>
@@ -6330,7 +6330,7 @@
         <v>1206.133911132812</v>
       </c>
       <c r="C421" t="n">
-        <v>842.0184936523438</v>
+        <v>842.0184326171875</v>
       </c>
       <c r="D421" t="n">
         <v>1771.26708984375</v>
@@ -6341,13 +6341,13 @@
         <v>45701</v>
       </c>
       <c r="B422" t="n">
-        <v>1205.687622070312</v>
+        <v>1205.687744140625</v>
       </c>
       <c r="C422" t="n">
         <v>837.5291137695312</v>
       </c>
       <c r="D422" t="n">
-        <v>1752.348388671875</v>
+        <v>1752.348510742188</v>
       </c>
     </row>
     <row r="423">
@@ -6361,7 +6361,7 @@
         <v>836.1231079101562</v>
       </c>
       <c r="D423" t="n">
-        <v>1764.849853515625</v>
+        <v>1764.849975585938</v>
       </c>
     </row>
     <row r="424">
@@ -6369,13 +6369,13 @@
         <v>45705</v>
       </c>
       <c r="B424" t="n">
-        <v>1214.412475585938</v>
+        <v>1214.412353515625</v>
       </c>
       <c r="C424" t="n">
         <v>847.2230834960938</v>
       </c>
       <c r="D424" t="n">
-        <v>1751.4453125</v>
+        <v>1751.445190429688</v>
       </c>
     </row>
     <row r="425">
@@ -6397,7 +6397,7 @@
         <v>45707</v>
       </c>
       <c r="B426" t="n">
-        <v>1216.9404296875</v>
+        <v>1216.940551757812</v>
       </c>
       <c r="C426" t="n">
         <v>852.0823974609375</v>
@@ -6439,13 +6439,13 @@
         <v>45712</v>
       </c>
       <c r="B429" t="n">
-        <v>1204.151123046875</v>
+        <v>1204.151000976562</v>
       </c>
       <c r="C429" t="n">
-        <v>827.3665161132812</v>
+        <v>827.366455078125</v>
       </c>
       <c r="D429" t="n">
-        <v>1677.101684570312</v>
+        <v>1677.101806640625</v>
       </c>
     </row>
     <row r="430">
@@ -6453,7 +6453,7 @@
         <v>45713</v>
       </c>
       <c r="B430" t="n">
-        <v>1193.69140625</v>
+        <v>1193.691284179688</v>
       </c>
       <c r="C430" t="n">
         <v>829.9564819335938</v>
@@ -6470,10 +6470,10 @@
         <v>1196.764770507812</v>
       </c>
       <c r="C431" t="n">
-        <v>839.0090942382812</v>
+        <v>839.0091552734375</v>
       </c>
       <c r="D431" t="n">
-        <v>1677.291870117188</v>
+        <v>1677.2919921875</v>
       </c>
     </row>
     <row r="432">
@@ -6487,7 +6487,7 @@
         <v>854.6477661132812</v>
       </c>
       <c r="D432" t="n">
-        <v>1604.469482421875</v>
+        <v>1604.469604492188</v>
       </c>
     </row>
     <row r="433">
@@ -6498,7 +6498,7 @@
         <v>1161.2216796875</v>
       </c>
       <c r="C433" t="n">
-        <v>839.4285278320312</v>
+        <v>839.428466796875</v>
       </c>
       <c r="D433" t="n">
         <v>1624.3388671875</v>
@@ -6515,7 +6515,7 @@
         <v>843.5971069335938</v>
       </c>
       <c r="D434" t="n">
-        <v>1605.039916992188</v>
+        <v>1605.0400390625</v>
       </c>
     </row>
     <row r="435">
@@ -6523,7 +6523,7 @@
         <v>45721</v>
       </c>
       <c r="B435" t="n">
-        <v>1165.534423828125</v>
+        <v>1165.534545898438</v>
       </c>
       <c r="C435" t="n">
         <v>833.73046875</v>
@@ -6537,7 +6537,7 @@
         <v>45722</v>
       </c>
       <c r="B436" t="n">
-        <v>1199.243286132812</v>
+        <v>1199.243408203125</v>
       </c>
       <c r="C436" t="n">
         <v>834.3224487304688</v>
@@ -6557,7 +6557,7 @@
         <v>833.3604736328125</v>
       </c>
       <c r="D437" t="n">
-        <v>1602.853271484375</v>
+        <v>1602.853393554688</v>
       </c>
     </row>
     <row r="438">
@@ -6565,7 +6565,7 @@
         <v>45726</v>
       </c>
       <c r="B438" t="n">
-        <v>1227.796875</v>
+        <v>1227.796752929688</v>
       </c>
       <c r="C438" t="n">
         <v>832.4971313476562</v>
@@ -6593,13 +6593,13 @@
         <v>45728</v>
       </c>
       <c r="B440" t="n">
-        <v>1246.287231445312</v>
+        <v>1246.287109375</v>
       </c>
       <c r="C440" t="n">
-        <v>844.1644897460938</v>
+        <v>844.1644287109375</v>
       </c>
       <c r="D440" t="n">
-        <v>1512.395751953125</v>
+        <v>1512.395629882812</v>
       </c>
     </row>
     <row r="441">
@@ -6607,10 +6607,10 @@
         <v>45729</v>
       </c>
       <c r="B441" t="n">
-        <v>1237.215454101562</v>
+        <v>1237.215576171875</v>
       </c>
       <c r="C441" t="n">
-        <v>841.9197387695312</v>
+        <v>841.9197998046875</v>
       </c>
       <c r="D441" t="n">
         <v>1501.938232421875</v>
@@ -6621,10 +6621,10 @@
         <v>45733</v>
       </c>
       <c r="B442" t="n">
-        <v>1228.242919921875</v>
+        <v>1228.242797851562</v>
       </c>
       <c r="C442" t="n">
-        <v>843.7944946289062</v>
+        <v>843.79443359375</v>
       </c>
       <c r="D442" t="n">
         <v>1511.63525390625</v>
@@ -6635,10 +6635,10 @@
         <v>45734</v>
       </c>
       <c r="B443" t="n">
-        <v>1228.242919921875</v>
+        <v>1228.242797851562</v>
       </c>
       <c r="C443" t="n">
-        <v>843.7944946289062</v>
+        <v>843.79443359375</v>
       </c>
       <c r="D443" t="n">
         <v>1511.63525390625</v>
@@ -6655,7 +6655,7 @@
         <v>860.4197387695312</v>
       </c>
       <c r="D444" t="n">
-        <v>1508.307983398438</v>
+        <v>1508.307861328125</v>
       </c>
     </row>
     <row r="445">
@@ -6663,10 +6663,10 @@
         <v>45736</v>
       </c>
       <c r="B445" t="n">
-        <v>1258.283447265625</v>
+        <v>1258.283569335938</v>
       </c>
       <c r="C445" t="n">
-        <v>872.580322265625</v>
+        <v>872.5803833007812</v>
       </c>
       <c r="D445" t="n">
         <v>1535.877807617188</v>
@@ -6677,13 +6677,13 @@
         <v>45737</v>
       </c>
       <c r="B446" t="n">
-        <v>1265.421875</v>
+        <v>1265.421752929688</v>
       </c>
       <c r="C446" t="n">
         <v>873.3696899414062</v>
       </c>
       <c r="D446" t="n">
-        <v>1514.011840820312</v>
+        <v>1514.012084960938</v>
       </c>
     </row>
     <row r="447">
@@ -6691,13 +6691,13 @@
         <v>45740</v>
       </c>
       <c r="B447" t="n">
-        <v>1290.951416015625</v>
+        <v>1290.951293945312</v>
       </c>
       <c r="C447" t="n">
         <v>887.9969482421875</v>
       </c>
       <c r="D447" t="n">
-        <v>1514.2021484375</v>
+        <v>1514.202026367188</v>
       </c>
     </row>
     <row r="448">
@@ -6725,7 +6725,7 @@
         <v>891.2283325195312</v>
       </c>
       <c r="D449" t="n">
-        <v>1520.571533203125</v>
+        <v>1520.571655273438</v>
       </c>
     </row>
     <row r="450">
@@ -6750,10 +6750,10 @@
         <v>1264.182495117188</v>
       </c>
       <c r="C451" t="n">
-        <v>901.9088745117188</v>
+        <v>901.908935546875</v>
       </c>
       <c r="D451" t="n">
-        <v>1493.19189453125</v>
+        <v>1493.192016601562</v>
       </c>
     </row>
     <row r="452">
@@ -6775,13 +6775,13 @@
         <v>45749</v>
       </c>
       <c r="B453" t="n">
-        <v>1240.437622070312</v>
+        <v>1240.437744140625</v>
       </c>
       <c r="C453" t="n">
         <v>886.4676513671875</v>
       </c>
       <c r="D453" t="n">
-        <v>1473.703125</v>
+        <v>1473.703002929688</v>
       </c>
     </row>
     <row r="454">
@@ -6789,13 +6789,13 @@
         <v>45750</v>
       </c>
       <c r="B454" t="n">
-        <v>1238.008544921875</v>
+        <v>1238.008666992188</v>
       </c>
       <c r="C454" t="n">
         <v>885.456298828125</v>
       </c>
       <c r="D454" t="n">
-        <v>1422.69873046875</v>
+        <v>1422.698608398438</v>
       </c>
     </row>
     <row r="455">
@@ -6806,10 +6806,10 @@
         <v>1194.38525390625</v>
       </c>
       <c r="C455" t="n">
-        <v>896.5316772460938</v>
+        <v>896.5316162109375</v>
       </c>
       <c r="D455" t="n">
-        <v>1380.060546875</v>
+        <v>1380.060668945312</v>
       </c>
     </row>
     <row r="456">
@@ -6817,13 +6817,13 @@
         <v>45754</v>
       </c>
       <c r="B456" t="n">
-        <v>1155.71923828125</v>
+        <v>1155.719116210938</v>
       </c>
       <c r="C456" t="n">
         <v>867.1289672851562</v>
       </c>
       <c r="D456" t="n">
-        <v>1327.868041992188</v>
+        <v>1327.867919921875</v>
       </c>
     </row>
     <row r="457">
@@ -6837,7 +6837,7 @@
         <v>872.7777099609375</v>
       </c>
       <c r="D457" t="n">
-        <v>1358.337524414062</v>
+        <v>1358.33740234375</v>
       </c>
     </row>
     <row r="458">
@@ -6876,7 +6876,7 @@
         <v>1229.482299804688</v>
       </c>
       <c r="C460" t="n">
-        <v>920.0142211914062</v>
+        <v>920.01416015625</v>
       </c>
       <c r="D460" t="n">
         <v>1355.675537109375</v>
@@ -6890,10 +6890,10 @@
         <v>1228.689208984375</v>
       </c>
       <c r="C461" t="n">
-        <v>926.4768676757812</v>
+        <v>926.476806640625</v>
       </c>
       <c r="D461" t="n">
-        <v>1343.41162109375</v>
+        <v>1343.411743164062</v>
       </c>
     </row>
     <row r="462">
@@ -6904,7 +6904,7 @@
         <v>1263.587768554688</v>
       </c>
       <c r="C462" t="n">
-        <v>940.6354370117188</v>
+        <v>940.6353759765625</v>
       </c>
       <c r="D462" t="n">
         <v>1349.49609375</v>
@@ -6915,7 +6915,7 @@
         <v>45768</v>
       </c>
       <c r="B463" t="n">
-        <v>1284.407958984375</v>
+        <v>1284.407836914062</v>
       </c>
       <c r="C463" t="n">
         <v>950.6994018554688</v>
@@ -6929,13 +6929,13 @@
         <v>45769</v>
       </c>
       <c r="B464" t="n">
-        <v>1280.144653320312</v>
+        <v>1280.144775390625</v>
       </c>
       <c r="C464" t="n">
         <v>967.7686767578125</v>
       </c>
       <c r="D464" t="n">
-        <v>1352.633422851562</v>
+        <v>1352.63330078125</v>
       </c>
     </row>
     <row r="465">
@@ -6946,7 +6946,7 @@
         <v>1288.869384765625</v>
       </c>
       <c r="C465" t="n">
-        <v>949.1207275390625</v>
+        <v>949.1207885742188</v>
       </c>
       <c r="D465" t="n">
         <v>1402.163940429688</v>
@@ -6963,7 +6963,7 @@
         <v>945.6181030273438</v>
       </c>
       <c r="D466" t="n">
-        <v>1398.836669921875</v>
+        <v>1398.836547851562</v>
       </c>
     </row>
     <row r="467">
@@ -6977,7 +6977,7 @@
         <v>942.8554077148438</v>
       </c>
       <c r="D467" t="n">
-        <v>1407.20263671875</v>
+        <v>1407.202514648438</v>
       </c>
     </row>
     <row r="468">
@@ -6985,7 +6985,7 @@
         <v>45775</v>
       </c>
       <c r="B468" t="n">
-        <v>1357.080322265625</v>
+        <v>1357.080444335938</v>
       </c>
       <c r="C468" t="n">
         <v>947.29541015625</v>
@@ -7002,7 +7002,7 @@
         <v>1387.715698242188</v>
       </c>
       <c r="C469" t="n">
-        <v>941.6714477539062</v>
+        <v>941.6715087890625</v>
       </c>
       <c r="D469" t="n">
         <v>1423.6494140625</v>
@@ -7019,7 +7019,7 @@
         <v>949.6633911132812</v>
       </c>
       <c r="D470" t="n">
-        <v>1426.121215820312</v>
+        <v>1426.12109375</v>
       </c>
     </row>
     <row r="471">
@@ -7030,10 +7030,10 @@
         <v>1407.643676757812</v>
       </c>
       <c r="C471" t="n">
-        <v>948.1341552734375</v>
+        <v>948.1340942382812</v>
       </c>
       <c r="D471" t="n">
-        <v>1432.5859375</v>
+        <v>1432.585815429688</v>
       </c>
     </row>
     <row r="472">
@@ -7072,10 +7072,10 @@
         <v>1393.961791992188</v>
       </c>
       <c r="C474" t="n">
-        <v>959.8260498046875</v>
+        <v>959.8259887695312</v>
       </c>
       <c r="D474" t="n">
-        <v>1433.916748046875</v>
+        <v>1433.916870117188</v>
       </c>
     </row>
     <row r="475">
@@ -7097,7 +7097,7 @@
         <v>45786</v>
       </c>
       <c r="B476" t="n">
-        <v>1365.408447265625</v>
+        <v>1365.408325195312</v>
       </c>
       <c r="C476" t="n">
         <v>932.248779296875</v>
@@ -7111,13 +7111,13 @@
         <v>45789</v>
       </c>
       <c r="B477" t="n">
-        <v>1424.20068359375</v>
+        <v>1424.200561523438</v>
       </c>
       <c r="C477" t="n">
-        <v>965.5487060546875</v>
+        <v>965.5486450195312</v>
       </c>
       <c r="D477" t="n">
-        <v>1546.667846679688</v>
+        <v>1546.66796875</v>
       </c>
     </row>
     <row r="478">
@@ -7125,10 +7125,10 @@
         <v>45790</v>
       </c>
       <c r="B478" t="n">
-        <v>1403.578735351562</v>
+        <v>1403.57861328125</v>
       </c>
       <c r="C478" t="n">
-        <v>948.4793701171875</v>
+        <v>948.4794311523438</v>
       </c>
       <c r="D478" t="n">
         <v>1491.243041992188</v>
@@ -7139,13 +7139,13 @@
         <v>45791</v>
       </c>
       <c r="B479" t="n">
-        <v>1412.204223632812</v>
+        <v>1412.204345703125</v>
       </c>
       <c r="C479" t="n">
         <v>942.5594482421875</v>
       </c>
       <c r="D479" t="n">
-        <v>1513.869262695312</v>
+        <v>1513.869384765625</v>
       </c>
     </row>
     <row r="480">
@@ -7159,7 +7159,7 @@
         <v>954.0047607421875</v>
       </c>
       <c r="D480" t="n">
-        <v>1533.453491210938</v>
+        <v>1533.453369140625</v>
       </c>
     </row>
     <row r="481">
@@ -7187,7 +7187,7 @@
         <v>956.4220581054688</v>
       </c>
       <c r="D482" t="n">
-        <v>1482.877075195312</v>
+        <v>1482.876953125</v>
       </c>
     </row>
     <row r="483">
@@ -7195,7 +7195,7 @@
         <v>45797</v>
       </c>
       <c r="B483" t="n">
-        <v>1412.402587890625</v>
+        <v>1412.402465820312</v>
       </c>
       <c r="C483" t="n">
         <v>944.6807861328125</v>
@@ -7209,13 +7209,13 @@
         <v>45798</v>
       </c>
       <c r="B484" t="n">
-        <v>1416.963134765625</v>
+        <v>1416.963012695312</v>
       </c>
       <c r="C484" t="n">
         <v>950.5514526367188</v>
       </c>
       <c r="D484" t="n">
-        <v>1491.148071289062</v>
+        <v>1491.14794921875</v>
       </c>
     </row>
     <row r="485">
@@ -7240,7 +7240,7 @@
         <v>1414.583862304688</v>
       </c>
       <c r="C486" t="n">
-        <v>953.9060668945312</v>
+        <v>953.906005859375</v>
       </c>
       <c r="D486" t="n">
         <v>1487.630493164062</v>
@@ -7254,10 +7254,10 @@
         <v>1422.515258789062</v>
       </c>
       <c r="C487" t="n">
-        <v>957.1619873046875</v>
+        <v>957.1620483398438</v>
       </c>
       <c r="D487" t="n">
-        <v>1502.55615234375</v>
+        <v>1502.556030273438</v>
       </c>
     </row>
     <row r="488">
@@ -7268,7 +7268,7 @@
         <v>1409.923950195312</v>
       </c>
       <c r="C488" t="n">
-        <v>950.3047485351562</v>
+        <v>950.3048095703125</v>
       </c>
       <c r="D488" t="n">
         <v>1492.669067382812</v>
@@ -7279,10 +7279,10 @@
         <v>45805</v>
       </c>
       <c r="B489" t="n">
-        <v>1400.802734375</v>
+        <v>1400.802856445312</v>
       </c>
       <c r="C489" t="n">
-        <v>948.9234008789062</v>
+        <v>948.9234619140625</v>
       </c>
       <c r="D489" t="n">
         <v>1494.285278320312</v>
@@ -7310,7 +7310,7 @@
         <v>1408.734252929688</v>
       </c>
       <c r="C491" t="n">
-        <v>959.480712890625</v>
+        <v>959.4807739257812</v>
       </c>
       <c r="D491" t="n">
         <v>1506.536987304688</v>
@@ -7324,7 +7324,7 @@
         <v>1401.595825195312</v>
       </c>
       <c r="C492" t="n">
-        <v>953.166015625</v>
+        <v>953.1660766601562</v>
       </c>
       <c r="D492" t="n">
         <v>1497.956909179688</v>
@@ -7335,7 +7335,7 @@
         <v>45811</v>
       </c>
       <c r="B493" t="n">
-        <v>1393.466186523438</v>
+        <v>1393.466064453125</v>
       </c>
       <c r="C493" t="n">
         <v>949.466064453125</v>
@@ -7349,10 +7349,10 @@
         <v>45812</v>
       </c>
       <c r="B494" t="n">
-        <v>1411.31201171875</v>
+        <v>1411.311889648438</v>
       </c>
       <c r="C494" t="n">
-        <v>957.6553344726562</v>
+        <v>957.6553955078125</v>
       </c>
       <c r="D494" t="n">
         <v>1495.450317382812</v>
@@ -7366,7 +7366,7 @@
         <v>1430.050170898438</v>
       </c>
       <c r="C495" t="n">
-        <v>961.79931640625</v>
+        <v>961.7993774414062</v>
       </c>
       <c r="D495" t="n">
         <v>1498.43896484375</v>
@@ -7377,7 +7377,7 @@
         <v>45814</v>
       </c>
       <c r="B496" t="n">
-        <v>1431.140747070312</v>
+        <v>1431.140625</v>
       </c>
       <c r="C496" t="n">
         <v>976.1552734375</v>
@@ -7394,7 +7394,7 @@
         <v>1436.395385742188</v>
       </c>
       <c r="C497" t="n">
-        <v>976.2540283203125</v>
+        <v>976.2539672851562</v>
       </c>
       <c r="D497" t="n">
         <v>1516.370483398438</v>
@@ -7422,7 +7422,7 @@
         <v>1436.494506835938</v>
       </c>
       <c r="C499" t="n">
-        <v>962.1940307617188</v>
+        <v>962.194091796875</v>
       </c>
       <c r="D499" t="n">
         <v>1572.478637695312</v>
@@ -7433,7 +7433,7 @@
         <v>45820</v>
       </c>
       <c r="B500" t="n">
-        <v>1429.257080078125</v>
+        <v>1429.256958007812</v>
       </c>
       <c r="C500" t="n">
         <v>958.74072265625</v>
@@ -7461,7 +7461,7 @@
         <v>45824</v>
       </c>
       <c r="B502" t="n">
-        <v>1425.489624023438</v>
+        <v>1425.489501953125</v>
       </c>
       <c r="C502" t="n">
         <v>954.7940673828125</v>
@@ -7475,7 +7475,7 @@
         <v>45825</v>
       </c>
       <c r="B503" t="n">
-        <v>1418.946044921875</v>
+        <v>1418.945922851562</v>
       </c>
       <c r="C503" t="n">
         <v>951.9327392578125</v>
@@ -7503,7 +7503,7 @@
         <v>45827</v>
       </c>
       <c r="B505" t="n">
-        <v>1421.028198242188</v>
+        <v>1421.028076171875</v>
       </c>
       <c r="C505" t="n">
         <v>954.7447509765625</v>
@@ -7534,7 +7534,7 @@
         <v>1444.326904296875</v>
       </c>
       <c r="C507" t="n">
-        <v>961.2073974609375</v>
+        <v>961.2073364257812</v>
       </c>
       <c r="D507" t="n">
         <v>1527.071533203125</v>
@@ -7545,7 +7545,7 @@
         <v>45832</v>
       </c>
       <c r="B508" t="n">
-        <v>1438.378295898438</v>
+        <v>1438.378173828125</v>
       </c>
       <c r="C508" t="n">
         <v>967.3740234375</v>
@@ -7573,10 +7573,10 @@
         <v>45834</v>
       </c>
       <c r="B510" t="n">
-        <v>1482.497314453125</v>
+        <v>1482.497192382812</v>
       </c>
       <c r="C510" t="n">
-        <v>997.4179077148438</v>
+        <v>997.41796875</v>
       </c>
       <c r="D510" t="n">
         <v>1557.921508789062</v>
@@ -7587,7 +7587,7 @@
         <v>45835</v>
       </c>
       <c r="B511" t="n">
-        <v>1502.425170898438</v>
+        <v>1502.425048828125</v>
       </c>
       <c r="C511" t="n">
         <v>1004.949157714844</v>
@@ -7629,7 +7629,7 @@
         <v>45840</v>
       </c>
       <c r="B514" t="n">
-        <v>1505.796020507812</v>
+        <v>1505.796142578125</v>
       </c>
       <c r="C514" t="n">
         <v>990.5350341796875</v>
@@ -7643,7 +7643,7 @@
         <v>45841</v>
       </c>
       <c r="B515" t="n">
-        <v>1504.8046875</v>
+        <v>1504.804565429688</v>
       </c>
       <c r="C515" t="n">
         <v>991.0836181640625</v>
@@ -7685,7 +7685,7 @@
         <v>45846</v>
       </c>
       <c r="B518" t="n">
-        <v>1524.434936523438</v>
+        <v>1524.43505859375</v>
       </c>
       <c r="C518" t="n">
         <v>998.2159423828125</v>
@@ -7713,7 +7713,7 @@
         <v>45848</v>
       </c>
       <c r="B520" t="n">
-        <v>1504.209594726562</v>
+        <v>1504.209716796875</v>
       </c>
       <c r="C520" t="n">
         <v>1000.609924316406</v>
@@ -7783,7 +7783,7 @@
         <v>45855</v>
       </c>
       <c r="B525" t="n">
-        <v>1463.759155273438</v>
+        <v>1463.759033203125</v>
       </c>
       <c r="C525" t="n">
         <v>990.98388671875</v>
@@ -7797,7 +7797,7 @@
         <v>45856</v>
       </c>
       <c r="B526" t="n">
-        <v>1463.362548828125</v>
+        <v>1463.362426757812</v>
       </c>
       <c r="C526" t="n">
         <v>976.2705078125</v>
@@ -7839,7 +7839,7 @@
         <v>45861</v>
       </c>
       <c r="B529" t="n">
-        <v>1412.402587890625</v>
+        <v>1412.402465820312</v>
       </c>
       <c r="C529" t="n">
         <v>1009.637512207031</v>
@@ -7853,7 +7853,7 @@
         <v>45862</v>
       </c>
       <c r="B530" t="n">
-        <v>1390.888427734375</v>
+        <v>1390.888305664062</v>
       </c>
       <c r="C530" t="n">
         <v>1004.599975585938</v>
@@ -7881,7 +7881,7 @@
         <v>45866</v>
       </c>
       <c r="B532" t="n">
-        <v>1375.71923828125</v>
+        <v>1375.719360351562</v>
       </c>
       <c r="C532" t="n">
         <v>1004.25</v>
@@ -7895,7 +7895,7 @@
         <v>45867</v>
       </c>
       <c r="B533" t="n">
-        <v>1404.966674804688</v>
+        <v>1404.966796875</v>
       </c>
       <c r="C533" t="n">
         <v>1010.799987792969</v>
@@ -7909,7 +7909,7 @@
         <v>45868</v>
       </c>
       <c r="B534" t="n">
-        <v>1398.026611328125</v>
+        <v>1398.026733398438</v>
       </c>
       <c r="C534" t="n">
         <v>1012.900024414062</v>
@@ -7979,7 +7979,7 @@
         <v>45875</v>
       </c>
       <c r="B539" t="n">
-        <v>1380.874755859375</v>
+        <v>1380.874877929688</v>
       </c>
       <c r="C539" t="n">
         <v>992.6500244140625</v>
@@ -7993,7 +7993,7 @@
         <v>45876</v>
       </c>
       <c r="B540" t="n">
-        <v>1377.504028320312</v>
+        <v>1377.50390625</v>
       </c>
       <c r="C540" t="n">
         <v>997.7000122070312</v>
